--- a/database/event/3460/event_3460_evp_summary.xlsx
+++ b/database/event/3460/event_3460_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.394</v>
+        <v>5.593</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8527</v>
+        <v>1.921</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7577</v>
+        <v>1.7843</v>
       </c>
       <c r="E2" t="n">
-        <v>5.394</v>
+        <v>5.593</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2821</v>
+        <v>2.1141</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1119</v>
+        <v>3.479</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2821</v>
+        <v>2.1141</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8497</v>
+        <v>1.7135</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1119</v>
+        <v>3.479</v>
       </c>
       <c r="K2" t="n">
         <v>102</v>
@@ -529,7 +529,7 @@
         <v>103</v>
       </c>
       <c r="M2" t="n">
-        <v>4.9616</v>
+        <v>5.1925</v>
       </c>
       <c r="N2" t="n">
         <v>205</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3783</v>
+        <v>5.394</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8473</v>
+        <v>1.8527</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7514</v>
+        <v>1.7051</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3783</v>
+        <v>5.394</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8993</v>
+        <v>2.2821</v>
       </c>
       <c r="G3" t="n">
-        <v>3.479</v>
+        <v>3.1119</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8993</v>
+        <v>2.2821</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5395</v>
+        <v>1.8497</v>
       </c>
       <c r="J3" t="n">
-        <v>3.479</v>
+        <v>3.1119</v>
       </c>
       <c r="K3" t="n">
         <v>102</v>
@@ -575,7 +575,7 @@
         <v>103</v>
       </c>
       <c r="M3" t="n">
-        <v>5.0185</v>
+        <v>4.9616</v>
       </c>
       <c r="N3" t="n">
         <v>205</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7402</v>
+        <v>5.3258</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6281</v>
+        <v>1.8293</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4936</v>
+        <v>1.6779</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7402</v>
+        <v>5.3258</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3669</v>
+        <v>2.9525</v>
       </c>
       <c r="G4" t="n">
         <v>2.3733</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3669</v>
+        <v>2.9525</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9185</v>
+        <v>2.3931</v>
       </c>
       <c r="J4" t="n">
         <v>2.3733</v>
@@ -621,7 +621,7 @@
         <v>111</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2918</v>
+        <v>4.7664</v>
       </c>
       <c r="N4" t="n">
         <v>162</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.1123</v>
+        <v>3.6775</v>
       </c>
       <c r="C5" t="n">
-        <v>1.069</v>
+        <v>1.2631</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8359</v>
+        <v>1.0212</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1123</v>
+        <v>3.6775</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0293</v>
+        <v>3.5945</v>
       </c>
       <c r="G5" t="n">
         <v>0.083</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0293</v>
+        <v>3.5945</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4553</v>
+        <v>2.9134</v>
       </c>
       <c r="J5" t="n">
         <v>0.083</v>
@@ -667,7 +667,7 @@
         <v>54</v>
       </c>
       <c r="M5" t="n">
-        <v>2.5383</v>
+        <v>2.9964</v>
       </c>
       <c r="N5" t="n">
         <v>146</v>
@@ -676,173 +676,173 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.0767</v>
+        <v>3.5046</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0568</v>
+        <v>1.2037</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8216</v>
+        <v>0.9523</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0767</v>
+        <v>3.5046</v>
       </c>
       <c r="F6" t="n">
-        <v>2.091</v>
+        <v>3.9445</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9857</v>
+        <v>-0.4399</v>
       </c>
       <c r="H6" t="n">
-        <v>2.091</v>
+        <v>3.9445</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6948</v>
+        <v>3.1971</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9857</v>
+        <v>-0.4399</v>
       </c>
       <c r="K6" t="n">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="L6" t="n">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6805</v>
+        <v>2.7572</v>
       </c>
       <c r="N6" t="n">
-        <v>205</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8653</v>
+        <v>3.0982</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9842</v>
+        <v>1.0641</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7362</v>
+        <v>0.7904</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8653</v>
+        <v>3.0982</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8395</v>
+        <v>2.6709</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0258</v>
+        <v>0.4273</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8395</v>
+        <v>2.6709</v>
       </c>
       <c r="I7" t="n">
-        <v>1.491</v>
+        <v>2.1648</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0258</v>
+        <v>0.4273</v>
       </c>
       <c r="K7" t="n">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="L7" t="n">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5168</v>
+        <v>2.5921</v>
       </c>
       <c r="N7" t="n">
-        <v>146</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.6403</v>
+        <v>3.0767</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9069</v>
+        <v>1.0568</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6453</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6403</v>
+        <v>3.0767</v>
       </c>
       <c r="F8" t="n">
-        <v>2.213</v>
+        <v>2.091</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4273</v>
+        <v>0.9857</v>
       </c>
       <c r="H8" t="n">
-        <v>2.213</v>
+        <v>2.091</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7937</v>
+        <v>1.6948</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4273</v>
+        <v>0.9857</v>
       </c>
       <c r="K8" t="n">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="L8" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M8" t="n">
-        <v>2.221</v>
+        <v>2.6805</v>
       </c>
       <c r="N8" t="n">
-        <v>162</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5144</v>
+        <v>2.9159</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8636</v>
+        <v>1.0015</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5944</v>
+        <v>0.7178</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5144</v>
+        <v>2.9159</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9543</v>
+        <v>3.5327</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4399</v>
+        <v>-0.6168</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9543</v>
+        <v>3.5327</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3946</v>
+        <v>2.8634</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4399</v>
+        <v>-0.6168</v>
       </c>
       <c r="K9" t="n">
         <v>44</v>
@@ -851,7 +851,7 @@
         <v>46</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9547</v>
+        <v>2.2466</v>
       </c>
       <c r="N9" t="n">
         <v>90</v>
@@ -860,47 +860,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4872</v>
+        <v>2.8653</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.9842</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5834</v>
+        <v>0.6976</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4872</v>
+        <v>2.8653</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2416</v>
+        <v>1.8395</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2456</v>
+        <v>1.0258</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2416</v>
+        <v>1.8395</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1958</v>
+        <v>1.491</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2456</v>
+        <v>1.0258</v>
       </c>
       <c r="K10" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="L10" t="n">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4414</v>
+        <v>2.5168</v>
       </c>
       <c r="N10" t="n">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1324</v>
+        <v>2.6648</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.9153</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4401</v>
+        <v>0.6177</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1324</v>
+        <v>2.6648</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7263</v>
+        <v>3.2587</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5939</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7263</v>
+        <v>3.2587</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2097</v>
+        <v>2.6412</v>
       </c>
       <c r="J11" t="n">
         <v>-0.5939</v>
@@ -943,7 +943,7 @@
         <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6158</v>
+        <v>2.0473</v>
       </c>
       <c r="N11" t="n">
         <v>146</v>
@@ -952,185 +952,185 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0674</v>
+        <v>2.4872</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7101</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4138</v>
+        <v>0.547</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0674</v>
+        <v>2.4872</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6842</v>
+        <v>0.2416</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6168</v>
+        <v>2.2456</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6842</v>
+        <v>0.2416</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1756</v>
+        <v>0.1958</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6168</v>
+        <v>2.2456</v>
       </c>
       <c r="K12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="L12" t="n">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5588</v>
+        <v>2.4414</v>
       </c>
       <c r="N12" t="n">
-        <v>90</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8609</v>
+        <v>1.9501</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6392</v>
+        <v>0.6698</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3304</v>
+        <v>0.333</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8609</v>
+        <v>1.9501</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3666</v>
+        <v>2.9501</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4943</v>
+        <v>-1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3666</v>
+        <v>2.9501</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2971</v>
+        <v>2.3911</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4943</v>
+        <v>-1</v>
       </c>
       <c r="K13" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="L13" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7914</v>
+        <v>1.3911</v>
       </c>
       <c r="N13" t="n">
-        <v>205</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8529</v>
+        <v>1.8609</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6364</v>
+        <v>0.6392</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3272</v>
+        <v>0.2975</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8529</v>
+        <v>1.8609</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8529</v>
+        <v>0.3666</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.4943</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8529</v>
+        <v>0.3666</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8529</v>
+        <v>0.2971</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.4943</v>
       </c>
       <c r="K14" t="n">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8529</v>
+        <v>1.7914</v>
       </c>
       <c r="N14" t="n">
-        <v>123</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5381</v>
+        <v>1.8529</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5283</v>
+        <v>0.6364</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2</v>
+        <v>0.2943</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5381</v>
+        <v>1.8529</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5381</v>
+        <v>1.8529</v>
       </c>
       <c r="G15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5381</v>
+        <v>1.8529</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0572</v>
+        <v>1.8529</v>
       </c>
       <c r="J15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="L15" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0572</v>
+        <v>1.8529</v>
       </c>
       <c r="N15" t="n">
-        <v>146</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -1146,7 +1146,7 @@
         <v>0.5217000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1922</v>
+        <v>0.1612</v>
       </c>
       <c r="E16" t="n">
         <v>1.5189</v>
@@ -1192,7 +1192,7 @@
         <v>0.4997</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1664</v>
+        <v>0.1357</v>
       </c>
       <c r="E17" t="n">
         <v>1.4549</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2241</v>
+        <v>1.2748</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4204</v>
+        <v>0.4379</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0731</v>
+        <v>0.064</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2241</v>
+        <v>1.2748</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3331</v>
+        <v>1.3838</v>
       </c>
       <c r="G18" t="n">
         <v>-0.109</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3331</v>
+        <v>1.3838</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0805</v>
+        <v>1.1216</v>
       </c>
       <c r="J18" t="n">
         <v>-0.109</v>
@@ -1265,7 +1265,7 @@
         <v>46</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9715</v>
+        <v>1.0126</v>
       </c>
       <c r="N18" t="n">
         <v>90</v>
@@ -1284,7 +1284,7 @@
         <v>0.334</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0285</v>
+        <v>-0.0565</v>
       </c>
       <c r="E19" t="n">
         <v>0.9724</v>
@@ -1320,124 +1320,124 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>cromen</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5312</v>
+        <v>0.5767</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1825</v>
+        <v>0.1981</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2068</v>
+        <v>-0.2142</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5312</v>
+        <v>0.5767</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5312</v>
+        <v>1.165</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.5883</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5312</v>
+        <v>1.165</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5312</v>
+        <v>0.9443</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.5883</v>
       </c>
       <c r="K20" t="n">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5312</v>
+        <v>0.356</v>
       </c>
       <c r="N20" t="n">
-        <v>113</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cromen</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.497</v>
+        <v>0.5725</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1707</v>
+        <v>0.1966</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2206</v>
+        <v>-0.2158</v>
       </c>
       <c r="E21" t="n">
-        <v>0.497</v>
+        <v>0.5725</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0853</v>
+        <v>1.3627</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5883</v>
+        <v>-0.7902</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0853</v>
+        <v>1.3627</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8797</v>
+        <v>1.1045</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5883</v>
+        <v>-0.7902</v>
       </c>
       <c r="K21" t="n">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="L21" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2914</v>
+        <v>0.3143</v>
       </c>
       <c r="N21" t="n">
-        <v>146</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3572</v>
+        <v>0.5312</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1227</v>
+        <v>0.1825</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2771</v>
+        <v>-0.2323</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3572</v>
+        <v>0.5312</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3572</v>
+        <v>0.5312</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3572</v>
+        <v>0.5312</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3572</v>
+        <v>0.5312</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3572</v>
+        <v>0.5312</v>
       </c>
       <c r="N22" t="n">
         <v>113</v>
@@ -1458,32 +1458,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3426</v>
+        <v>0.3572</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1177</v>
+        <v>0.1227</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.283</v>
+        <v>-0.3016</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3426</v>
+        <v>0.3572</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3426</v>
+        <v>0.3572</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3426</v>
+        <v>0.3572</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3426</v>
+        <v>0.3572</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3426</v>
+        <v>0.3572</v>
       </c>
       <c r="N23" t="n">
         <v>113</v>
@@ -1504,139 +1504,139 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1752</v>
+        <v>0.3426</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0602</v>
+        <v>0.1177</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3506</v>
+        <v>-0.3074</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1752</v>
+        <v>0.3426</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1752</v>
+        <v>0.3426</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1752</v>
+        <v>0.3426</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1752</v>
+        <v>0.3426</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1752</v>
+        <v>0.3426</v>
       </c>
       <c r="N24" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1207</v>
+        <v>0.1752</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0415</v>
+        <v>0.0602</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3726</v>
+        <v>-0.3741</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1207</v>
+        <v>0.1752</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1207</v>
+        <v>0.1752</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1207</v>
+        <v>0.1752</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1207</v>
+        <v>0.1752</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1207</v>
+        <v>0.1752</v>
       </c>
       <c r="N25" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1058</v>
+        <v>0.1207</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0363</v>
+        <v>0.0415</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3786</v>
+        <v>-0.3958</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1058</v>
+        <v>0.1207</v>
       </c>
       <c r="F26" t="n">
-        <v>0.896</v>
+        <v>0.1207</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.7902</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.896</v>
+        <v>0.1207</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.1207</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7902</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>44</v>
+        <v>164</v>
       </c>
       <c r="L26" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.06390000000000007</v>
+        <v>0.1207</v>
       </c>
       <c r="N26" t="n">
-        <v>90</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27">
@@ -1652,7 +1652,7 @@
         <v>-0.0124</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4359</v>
+        <v>-0.4583</v>
       </c>
       <c r="E27" t="n">
         <v>-0.0361</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0391</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4674</v>
+        <v>-0.4893</v>
       </c>
       <c r="E28" t="n">
         <v>-0.1139</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0503</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4805</v>
+        <v>-0.5023</v>
       </c>
       <c r="E29" t="n">
         <v>-0.1465</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0799</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5154</v>
+        <v>-0.5366</v>
       </c>
       <c r="E30" t="n">
         <v>-0.2327</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1034</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.543</v>
+        <v>-0.5638</v>
       </c>
       <c r="E31" t="n">
         <v>-0.301</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1833</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.637</v>
+        <v>-0.6566</v>
       </c>
       <c r="E32" t="n">
         <v>-0.5338000000000001</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2068</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6646</v>
+        <v>-0.6837</v>
       </c>
       <c r="E33" t="n">
         <v>-0.602</v>
@@ -1974,7 +1974,7 @@
         <v>-0.2663</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7346</v>
+        <v>-0.7528</v>
       </c>
       <c r="E34" t="n">
         <v>-0.7753</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3433</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8250999999999999</v>
+        <v>-0.8421</v>
       </c>
       <c r="E35" t="n">
         <v>-0.9995000000000001</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3972</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8885</v>
+        <v>-0.9046</v>
       </c>
       <c r="E36" t="n">
         <v>-1.1563</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4257</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9221</v>
+        <v>-0.9377</v>
       </c>
       <c r="E37" t="n">
         <v>-1.2394</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4297</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9267</v>
+        <v>-0.9423</v>
       </c>
       <c r="E38" t="n">
         <v>-1.2509</v>
@@ -2204,7 +2204,7 @@
         <v>-0.5366</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0525</v>
+        <v>-1.0663</v>
       </c>
       <c r="E39" t="n">
         <v>-1.5622</v>
@@ -2250,7 +2250,7 @@
         <v>-0.5898</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.115</v>
+        <v>-1.128</v>
       </c>
       <c r="E40" t="n">
         <v>-1.7171</v>
@@ -2296,7 +2296,7 @@
         <v>-0.8211000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3872</v>
+        <v>-1.3964</v>
       </c>
       <c r="E41" t="n">
         <v>-2.3907</v>

--- a/database/event/3460/event_3460_evp_summary.xlsx
+++ b/database/event/3460/event_3460_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.593</v>
+        <v>5.7174</v>
       </c>
       <c r="C2" t="n">
-        <v>1.921</v>
+        <v>1.9638</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7843</v>
+        <v>1.9431</v>
       </c>
       <c r="E2" t="n">
-        <v>5.593</v>
+        <v>5.7174</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1141</v>
+        <v>2.6118</v>
       </c>
       <c r="G2" t="n">
-        <v>3.479</v>
+        <v>3.1056</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1141</v>
+        <v>3.7159</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7135</v>
+        <v>1.9321</v>
       </c>
       <c r="J2" t="n">
-        <v>3.479</v>
+        <v>3.1056</v>
       </c>
       <c r="K2" t="n">
         <v>102</v>
@@ -529,7 +529,7 @@
         <v>103</v>
       </c>
       <c r="M2" t="n">
-        <v>5.1925</v>
+        <v>5.0377</v>
       </c>
       <c r="N2" t="n">
         <v>205</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.394</v>
+        <v>5.5333</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8527</v>
+        <v>1.9005</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7051</v>
+        <v>1.86</v>
       </c>
       <c r="E3" t="n">
-        <v>5.394</v>
+        <v>5.5333</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2821</v>
+        <v>2.6715</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1119</v>
+        <v>2.8618</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2821</v>
+        <v>3.9263</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8497</v>
+        <v>2.0415</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1119</v>
+        <v>2.8618</v>
       </c>
       <c r="K3" t="n">
         <v>102</v>
@@ -575,7 +575,7 @@
         <v>103</v>
       </c>
       <c r="M3" t="n">
-        <v>4.9616</v>
+        <v>4.9033</v>
       </c>
       <c r="N3" t="n">
         <v>205</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3258</v>
+        <v>4.6378</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8293</v>
+        <v>1.593</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6779</v>
+        <v>1.4557</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3258</v>
+        <v>4.6378</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9525</v>
+        <v>2.7503</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3733</v>
+        <v>1.8875</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9525</v>
+        <v>4.2039</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3931</v>
+        <v>2.1858</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3733</v>
+        <v>1.8875</v>
       </c>
       <c r="K4" t="n">
         <v>51</v>
@@ -621,7 +621,7 @@
         <v>111</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7664</v>
+        <v>4.0733</v>
       </c>
       <c r="N4" t="n">
         <v>162</v>
@@ -630,219 +630,219 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6775</v>
+        <v>3.6301</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2631</v>
+        <v>1.2468</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0212</v>
+        <v>1.0008</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6775</v>
+        <v>3.6301</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5945</v>
+        <v>2.4827</v>
       </c>
       <c r="G5" t="n">
-        <v>0.083</v>
+        <v>1.1474</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5945</v>
+        <v>3.2611</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9134</v>
+        <v>1.6956</v>
       </c>
       <c r="J5" t="n">
-        <v>0.083</v>
+        <v>1.1474</v>
       </c>
       <c r="K5" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="L5" t="n">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9964</v>
+        <v>2.843</v>
       </c>
       <c r="N5" t="n">
-        <v>146</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5046</v>
+        <v>3.4609</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2037</v>
+        <v>1.1887</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9523</v>
+        <v>0.9244</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5046</v>
+        <v>3.4609</v>
       </c>
       <c r="F6" t="n">
-        <v>3.9445</v>
+        <v>2.4716</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4399</v>
+        <v>0.9893</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9445</v>
+        <v>3.222</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1971</v>
+        <v>1.6753</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4399</v>
+        <v>0.9893</v>
       </c>
       <c r="K6" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="L6" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7572</v>
+        <v>2.6646</v>
       </c>
       <c r="N6" t="n">
-        <v>90</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.0982</v>
+        <v>3.3669</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0641</v>
+        <v>1.1564</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7904</v>
+        <v>0.882</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0982</v>
+        <v>3.3669</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6709</v>
+        <v>3.1841</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4273</v>
+        <v>0.1828</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6709</v>
+        <v>5.7325</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1648</v>
+        <v>2.9806</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4273</v>
+        <v>0.1828</v>
       </c>
       <c r="K7" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="L7" t="n">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5921</v>
+        <v>3.1634</v>
       </c>
       <c r="N7" t="n">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0767</v>
+        <v>3.2266</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0568</v>
+        <v>1.1083</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.8186</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0767</v>
+        <v>3.2266</v>
       </c>
       <c r="F8" t="n">
-        <v>2.091</v>
+        <v>2.7082</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9857</v>
+        <v>0.5184</v>
       </c>
       <c r="H8" t="n">
-        <v>2.091</v>
+        <v>4.0556</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6948</v>
+        <v>2.1087</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9857</v>
+        <v>0.5184</v>
       </c>
       <c r="K8" t="n">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="L8" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6805</v>
+        <v>2.6271</v>
       </c>
       <c r="N8" t="n">
-        <v>205</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9159</v>
+        <v>2.7513</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0015</v>
+        <v>0.945</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7178</v>
+        <v>0.6041</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9159</v>
+        <v>2.7513</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5327</v>
+        <v>3.105</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6168</v>
+        <v>-0.3537</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5327</v>
+        <v>5.4539</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8634</v>
+        <v>2.8358</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6168</v>
+        <v>-0.3537</v>
       </c>
       <c r="K9" t="n">
         <v>44</v>
@@ -851,7 +851,7 @@
         <v>46</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2466</v>
+        <v>2.4821</v>
       </c>
       <c r="N9" t="n">
         <v>90</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8653</v>
+        <v>2.6879</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9842</v>
+        <v>0.9232</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6976</v>
+        <v>0.5754</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8653</v>
+        <v>2.6879</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8395</v>
+        <v>3.0683</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0258</v>
+        <v>-0.3804</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8395</v>
+        <v>5.3245</v>
       </c>
       <c r="I10" t="n">
-        <v>1.491</v>
+        <v>2.7685</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0258</v>
+        <v>-0.3804</v>
       </c>
       <c r="K10" t="n">
         <v>92</v>
@@ -897,7 +897,7 @@
         <v>54</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5168</v>
+        <v>2.3881</v>
       </c>
       <c r="N10" t="n">
         <v>146</v>
@@ -906,47 +906,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6648</v>
+        <v>2.5264</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9153</v>
+        <v>0.8678</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6177</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6648</v>
+        <v>2.5264</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2587</v>
+        <v>2.9697</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5939</v>
+        <v>-0.4433</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2587</v>
+        <v>4.9771</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6412</v>
+        <v>2.5878</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5939</v>
+        <v>-0.4433</v>
       </c>
       <c r="K11" t="n">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="L11" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0473</v>
+        <v>2.1445</v>
       </c>
       <c r="N11" t="n">
-        <v>146</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4872</v>
+        <v>2.4805</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.852</v>
       </c>
       <c r="D12" t="n">
-        <v>0.547</v>
+        <v>0.4818</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4872</v>
+        <v>2.4805</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2416</v>
+        <v>0.6976</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2456</v>
+        <v>1.7829</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2416</v>
+        <v>0.6976</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1958</v>
+        <v>0.3627</v>
       </c>
       <c r="J12" t="n">
-        <v>2.2456</v>
+        <v>1.7829</v>
       </c>
       <c r="K12" t="n">
         <v>51</v>
@@ -989,7 +989,7 @@
         <v>111</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4414</v>
+        <v>2.1456</v>
       </c>
       <c r="N12" t="n">
         <v>162</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9501</v>
+        <v>2.4121</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6698</v>
+        <v>0.8285</v>
       </c>
       <c r="D13" t="n">
-        <v>0.333</v>
+        <v>0.4509</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9501</v>
+        <v>2.4121</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9501</v>
+        <v>1.1182</v>
       </c>
       <c r="G13" t="n">
-        <v>-1</v>
+        <v>1.2939</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9501</v>
+        <v>1.1182</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3911</v>
+        <v>0.5814</v>
       </c>
       <c r="J13" t="n">
-        <v>-1</v>
+        <v>1.2939</v>
       </c>
       <c r="K13" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="L13" t="n">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3911</v>
+        <v>1.8753</v>
       </c>
       <c r="N13" t="n">
-        <v>146</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8609</v>
+        <v>2.356</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6392</v>
+        <v>0.8092</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2975</v>
+        <v>0.4256</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8609</v>
+        <v>2.356</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3666</v>
+        <v>2.2914</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4943</v>
+        <v>0.0646</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3666</v>
+        <v>2.5872</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2971</v>
+        <v>1.3452</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4943</v>
+        <v>0.0646</v>
       </c>
       <c r="K14" t="n">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="L14" t="n">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7914</v>
+        <v>1.4098</v>
       </c>
       <c r="N14" t="n">
-        <v>205</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8529</v>
+        <v>2.201</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6364</v>
+        <v>0.756</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2943</v>
+        <v>0.3556</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8529</v>
+        <v>2.201</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8529</v>
+        <v>2.201</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8529</v>
+        <v>2.201</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8529</v>
+        <v>2.201</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8529</v>
+        <v>2.201</v>
       </c>
       <c r="N15" t="n">
         <v>123</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5189</v>
+        <v>2.0869</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.7168</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1612</v>
+        <v>0.3041</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5189</v>
+        <v>2.0869</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4611</v>
+        <v>1.0159</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0578</v>
+        <v>1.071</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4611</v>
+        <v>1.0159</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3737</v>
+        <v>0.5282</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0578</v>
+        <v>1.071</v>
       </c>
       <c r="K16" t="n">
         <v>51</v>
@@ -1173,7 +1173,7 @@
         <v>111</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4315</v>
+        <v>1.5992</v>
       </c>
       <c r="N16" t="n">
         <v>162</v>
@@ -1182,262 +1182,262 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4549</v>
+        <v>2.0286</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4997</v>
+        <v>0.6968</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1357</v>
+        <v>0.2778</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4549</v>
+        <v>2.0286</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4549</v>
+        <v>2.9444</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4549</v>
+        <v>4.8879</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4549</v>
+        <v>2.5415</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>164</v>
+        <v>92</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4549</v>
+        <v>1.6257</v>
       </c>
       <c r="N17" t="n">
-        <v>164</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>cromen</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2748</v>
+        <v>1.9437</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4379</v>
+        <v>0.6676</v>
       </c>
       <c r="D18" t="n">
-        <v>0.064</v>
+        <v>0.2395</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2748</v>
+        <v>1.9437</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3838</v>
+        <v>2.3212</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.109</v>
+        <v>-0.3775</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3838</v>
+        <v>2.6922</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1216</v>
+        <v>1.3998</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.109</v>
+        <v>-0.3775</v>
       </c>
       <c r="K18" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="L18" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0126</v>
+        <v>1.0223</v>
       </c>
       <c r="N18" t="n">
-        <v>90</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9724</v>
+        <v>1.4785</v>
       </c>
       <c r="C19" t="n">
-        <v>0.334</v>
+        <v>0.5078</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0565</v>
+        <v>0.0295</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9724</v>
+        <v>1.4785</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9724</v>
+        <v>1.4785</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9724</v>
+        <v>1.4785</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9724</v>
+        <v>1.4785</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9724</v>
+        <v>1.4785</v>
       </c>
       <c r="N19" t="n">
-        <v>113</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cromen</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5767</v>
+        <v>1.4159</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1981</v>
+        <v>0.4863</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2142</v>
+        <v>0.0012</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5767</v>
+        <v>1.4159</v>
       </c>
       <c r="F20" t="n">
-        <v>1.165</v>
+        <v>1.9781</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5883</v>
+        <v>-0.5622</v>
       </c>
       <c r="H20" t="n">
-        <v>1.165</v>
+        <v>1.9781</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9443</v>
+        <v>1.0285</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5883</v>
+        <v>-0.5622</v>
       </c>
       <c r="K20" t="n">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="L20" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="M20" t="n">
-        <v>0.356</v>
+        <v>0.4662999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>146</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5725</v>
+        <v>1.1945</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1966</v>
+        <v>0.4103</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2158</v>
+        <v>-0.0988</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5725</v>
+        <v>1.1945</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3627</v>
+        <v>2.262</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7902</v>
+        <v>-1.0675</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3627</v>
+        <v>2.4835</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1045</v>
+        <v>1.2913</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7902</v>
+        <v>-1.0675</v>
       </c>
       <c r="K21" t="n">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="L21" t="n">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3143</v>
+        <v>0.2238</v>
       </c>
       <c r="N21" t="n">
-        <v>90</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5312</v>
+        <v>1.0591</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1825</v>
+        <v>0.3638</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2323</v>
+        <v>-0.1599</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5312</v>
+        <v>1.0591</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5312</v>
+        <v>1.0591</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5312</v>
+        <v>1.0591</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5312</v>
+        <v>1.0591</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5312</v>
+        <v>1.0591</v>
       </c>
       <c r="N22" t="n">
         <v>113</v>
@@ -1458,32 +1458,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3572</v>
+        <v>0.8185</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1227</v>
+        <v>0.2811</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3016</v>
+        <v>-0.2685</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3572</v>
+        <v>0.8185</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3572</v>
+        <v>0.8185</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3572</v>
+        <v>0.8185</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3572</v>
+        <v>0.8185</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3572</v>
+        <v>0.8185</v>
       </c>
       <c r="N23" t="n">
         <v>113</v>
@@ -1504,32 +1504,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3426</v>
+        <v>0.7509</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1177</v>
+        <v>0.2579</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3074</v>
+        <v>-0.299</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3426</v>
+        <v>0.7509</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3426</v>
+        <v>0.7509</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3426</v>
+        <v>0.7509</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3426</v>
+        <v>0.7509</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3426</v>
+        <v>0.7509</v>
       </c>
       <c r="N24" t="n">
         <v>113</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1752</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0602</v>
+        <v>0.2187</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3741</v>
+        <v>-0.3506</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1752</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1752</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1752</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1752</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1752</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>123</v>
@@ -1596,78 +1596,78 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1207</v>
+        <v>0.4988</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0415</v>
+        <v>0.1713</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3958</v>
+        <v>-0.4128</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1207</v>
+        <v>0.4988</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1207</v>
+        <v>0.4988</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1207</v>
+        <v>0.4988</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1207</v>
+        <v>0.4988</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1207</v>
+        <v>0.4988</v>
       </c>
       <c r="N26" t="n">
-        <v>164</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0361</v>
+        <v>0.3339</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0124</v>
+        <v>0.1147</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4583</v>
+        <v>-0.4873</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0361</v>
+        <v>0.3339</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0361</v>
+        <v>0.3339</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0361</v>
+        <v>0.3339</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0361</v>
+        <v>0.3339</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0361</v>
+        <v>0.3339</v>
       </c>
       <c r="N27" t="n">
         <v>123</v>
@@ -1688,323 +1688,323 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1139</v>
+        <v>0.2697</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0391</v>
+        <v>0.0926</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4893</v>
+        <v>-0.5163</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1139</v>
+        <v>0.2697</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1139</v>
+        <v>0.2697</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1139</v>
+        <v>0.2697</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1139</v>
+        <v>0.2697</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1139</v>
+        <v>0.2697</v>
       </c>
       <c r="N28" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1465</v>
+        <v>0.237</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0503</v>
+        <v>0.0814</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5023</v>
+        <v>-0.531</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1465</v>
+        <v>0.237</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1465</v>
+        <v>0.237</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1465</v>
+        <v>0.237</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1465</v>
+        <v>0.237</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1465</v>
+        <v>0.237</v>
       </c>
       <c r="N29" t="n">
-        <v>123</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2327</v>
+        <v>0.199</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0799</v>
+        <v>0.0684</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5366</v>
+        <v>-0.5482</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2327</v>
+        <v>0.199</v>
       </c>
       <c r="F30" t="n">
-        <v>1.2536</v>
+        <v>0.9939</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.4863</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>1.2536</v>
+        <v>0.9939</v>
       </c>
       <c r="I30" t="n">
-        <v>1.0161</v>
+        <v>0.5168</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.4863</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="L30" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4702</v>
+        <v>-0.2781</v>
       </c>
       <c r="N30" t="n">
-        <v>205</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NEKIZ</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.301</v>
+        <v>0.1206</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1034</v>
+        <v>0.0414</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5638</v>
+        <v>-0.5836</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.301</v>
+        <v>0.1206</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.301</v>
+        <v>0.1206</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.301</v>
+        <v>0.1206</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.301</v>
+        <v>0.1206</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.301</v>
+        <v>0.1206</v>
       </c>
       <c r="N31" t="n">
-        <v>69</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>NEKIZ</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5338000000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1833</v>
+        <v>0.0238</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6566</v>
+        <v>-0.6067</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5338000000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5338000000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5338000000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5338000000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5338000000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="N32" t="n">
-        <v>113</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.602</v>
+        <v>-0.0489</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2068</v>
+        <v>-0.0168</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6837</v>
+        <v>-0.6601</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.602</v>
+        <v>-0.0489</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4453</v>
+        <v>0.7056</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.0473</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4453</v>
+        <v>0.7056</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3609</v>
+        <v>0.3669</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.0473</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="L33" t="n">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6863999999999999</v>
+        <v>-0.3875999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>162</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7753</v>
+        <v>-0.3235</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2663</v>
+        <v>-0.1111</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7528</v>
+        <v>-0.7841</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7753</v>
+        <v>-0.3235</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2247</v>
+        <v>-0.3235</v>
       </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2247</v>
+        <v>-0.3235</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1821</v>
+        <v>-0.3235</v>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="L34" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8179</v>
+        <v>-0.3235</v>
       </c>
       <c r="N34" t="n">
-        <v>90</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9995000000000001</v>
+        <v>-0.7117</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3433</v>
+        <v>-0.2445</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8421</v>
+        <v>-0.9593</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9995000000000001</v>
+        <v>-0.7117</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9995000000000001</v>
+        <v>-0.7117</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9995000000000001</v>
+        <v>-0.7117</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9995000000000001</v>
+        <v>-0.7117</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9995000000000001</v>
+        <v>-0.7117</v>
       </c>
       <c r="N35" t="n">
         <v>69</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1563</v>
+        <v>-0.7934</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3972</v>
+        <v>-0.2725</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9046</v>
+        <v>-0.9962</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1563</v>
+        <v>-0.7934</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1563</v>
+        <v>-0.7934</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1563</v>
+        <v>-0.7934</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1563</v>
+        <v>-0.7934</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1563</v>
+        <v>-0.7934</v>
       </c>
       <c r="N36" t="n">
-        <v>69</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2394</v>
+        <v>-0.8293</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4257</v>
+        <v>-0.2848</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9377</v>
+        <v>-1.0124</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2394</v>
+        <v>-0.8293</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2394</v>
+        <v>-0.8293</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2394</v>
+        <v>-0.8293</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2394</v>
+        <v>-0.8293</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>164</v>
+        <v>69</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2394</v>
+        <v>-0.8293</v>
       </c>
       <c r="N37" t="n">
-        <v>164</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2509</v>
+        <v>-0.8771</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4297</v>
+        <v>-0.3013</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9423</v>
+        <v>-1.034</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2509</v>
+        <v>-0.8771</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2509</v>
+        <v>-0.8771</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2509</v>
+        <v>-0.8771</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2509</v>
+        <v>-0.8771</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2509</v>
+        <v>-0.8771</v>
       </c>
       <c r="N38" t="n">
         <v>69</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5622</v>
+        <v>-0.8863</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5366</v>
+        <v>-0.3044</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0663</v>
+        <v>-1.0381</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5622</v>
+        <v>-0.8863</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5622</v>
+        <v>-0.8863</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5622</v>
+        <v>-0.8863</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5622</v>
+        <v>-0.8863</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5622</v>
+        <v>-0.8863</v>
       </c>
       <c r="N39" t="n">
         <v>123</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7171</v>
+        <v>-1.1719</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5898</v>
+        <v>-0.4025</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.128</v>
+        <v>-1.1671</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7171</v>
+        <v>-1.1719</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7171</v>
+        <v>-1.1719</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7171</v>
+        <v>-1.1719</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7171</v>
+        <v>-1.1719</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7171</v>
+        <v>-1.1719</v>
       </c>
       <c r="N40" t="n">
         <v>69</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.3907</v>
+        <v>-1.6107</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.5532</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3964</v>
+        <v>-1.3652</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.3907</v>
+        <v>-1.6107</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.3907</v>
+        <v>-1.6107</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.3907</v>
+        <v>-1.6107</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.3907</v>
+        <v>-1.6107</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.3907</v>
+        <v>-1.6107</v>
       </c>
       <c r="N41" t="n">
         <v>164</v>
@@ -2429,10 +2429,10 @@
         <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.8547</v>
       </c>
       <c r="J2" t="n">
-        <v>20.73</v>
+        <v>25.641</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6077</v>
+        <v>0.7428</v>
       </c>
       <c r="J3" t="n">
-        <v>18.231</v>
+        <v>22.284</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.12</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2054</v>
+        <v>0.2637</v>
       </c>
       <c r="J4" t="n">
-        <v>6.162</v>
+        <v>7.911</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0297</v>
+        <v>0.0738</v>
       </c>
       <c r="J5" t="n">
-        <v>0.891</v>
+        <v>2.214</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.58</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6843</v>
+        <v>-0.4585</v>
       </c>
       <c r="J6" t="n">
-        <v>-20.529</v>
+        <v>-13.755</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8764</v>
+        <v>0.8486</v>
       </c>
       <c r="J7" t="n">
-        <v>26.292</v>
+        <v>25.458</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.533</v>
+        <v>0.4965</v>
       </c>
       <c r="J8" t="n">
-        <v>15.99</v>
+        <v>14.895</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.98</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1554</v>
+        <v>-0.1056</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.662</v>
+        <v>-3.168</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.91</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3922</v>
+        <v>-0.334</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.766</v>
+        <v>-10.02</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.9</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4215</v>
+        <v>-0.3632</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.645</v>
+        <v>-10.896</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.55</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7958</v>
+        <v>0.9883</v>
       </c>
       <c r="J12" t="n">
-        <v>21.4866</v>
+        <v>26.6841</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3572</v>
+        <v>0.4174</v>
       </c>
       <c r="J13" t="n">
-        <v>9.644399999999999</v>
+        <v>11.2698</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1088</v>
+        <v>0.1504</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9376</v>
+        <v>4.0608</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.8</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3994</v>
+        <v>-0.2475</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.7838</v>
+        <v>-6.6825</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.77</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4408</v>
+        <v>-0.2772</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.9016</v>
+        <v>-7.4844</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.53</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3264</v>
+        <v>1.2049</v>
       </c>
       <c r="J17" t="n">
-        <v>35.8128</v>
+        <v>32.5323</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.17</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5191</v>
+        <v>0.5039</v>
       </c>
       <c r="J18" t="n">
-        <v>14.0157</v>
+        <v>13.6053</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.02</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0171</v>
+        <v>0.0696</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4617</v>
+        <v>1.8792</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3279</v>
+        <v>-0.2597</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.853300000000001</v>
+        <v>-7.0119</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.9</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.447</v>
+        <v>-0.3805</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.069</v>
+        <v>-10.2735</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.32</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9363</v>
+        <v>0.6733</v>
       </c>
       <c r="J22" t="n">
-        <v>28.089</v>
+        <v>20.199</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.07</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2853</v>
+        <v>0.2529</v>
       </c>
       <c r="J23" t="n">
-        <v>8.558999999999999</v>
+        <v>7.587</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.02</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0833</v>
+        <v>0.0895</v>
       </c>
       <c r="J24" t="n">
-        <v>2.499</v>
+        <v>2.685</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.87</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4943</v>
+        <v>-0.4407</v>
       </c>
       <c r="J25" t="n">
-        <v>-14.829</v>
+        <v>-13.221</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.84</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5749</v>
+        <v>-0.5226</v>
       </c>
       <c r="J26" t="n">
-        <v>-17.247</v>
+        <v>-15.678</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.31</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5299</v>
+        <v>0.5088</v>
       </c>
       <c r="J27" t="n">
-        <v>15.897</v>
+        <v>15.264</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.22</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4086</v>
+        <v>0.4153</v>
       </c>
       <c r="J28" t="n">
-        <v>12.258</v>
+        <v>12.459</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.97</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0968</v>
+        <v>-0.0509</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.904</v>
+        <v>-1.527</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1779</v>
+        <v>-0.1011</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.337</v>
+        <v>-3.033</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.62</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6229</v>
+        <v>-0.4119</v>
       </c>
       <c r="J31" t="n">
-        <v>-18.687</v>
+        <v>-12.357</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.73</v>
       </c>
       <c r="I32" t="n">
-        <v>1.6122</v>
+        <v>1.1273</v>
       </c>
       <c r="J32" t="n">
-        <v>38.6928</v>
+        <v>27.0552</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.42</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0076</v>
+        <v>0.7461</v>
       </c>
       <c r="J33" t="n">
-        <v>24.1824</v>
+        <v>17.9064</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.17</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3811</v>
+        <v>0.4124</v>
       </c>
       <c r="J34" t="n">
-        <v>9.1464</v>
+        <v>9.897600000000001</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.13</v>
       </c>
       <c r="I35" t="n">
-        <v>0.277</v>
+        <v>0.3506</v>
       </c>
       <c r="J35" t="n">
-        <v>6.648</v>
+        <v>8.414400000000001</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.04</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0151</v>
+        <v>0.0956</v>
       </c>
       <c r="J36" t="n">
-        <v>0.3624</v>
+        <v>2.2944</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.22</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4959</v>
+        <v>0.4805</v>
       </c>
       <c r="J37" t="n">
-        <v>11.9016</v>
+        <v>11.532</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.78</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3256</v>
+        <v>-0.2325</v>
       </c>
       <c r="J38" t="n">
-        <v>-7.8144</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.73</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.416</v>
+        <v>-0.2793</v>
       </c>
       <c r="J39" t="n">
-        <v>-9.984</v>
+        <v>-6.7032</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.68</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4915</v>
+        <v>-0.3266</v>
       </c>
       <c r="J40" t="n">
-        <v>-11.796</v>
+        <v>-7.8384</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.49</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.743</v>
+        <v>-0.5039</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.832</v>
+        <v>-12.0936</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>0.85</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.181</v>
+        <v>-0.1566</v>
       </c>
       <c r="J42" t="n">
-        <v>-3.982</v>
+        <v>-3.4452</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.79</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2807</v>
+        <v>-0.2189</v>
       </c>
       <c r="J43" t="n">
-        <v>-6.1754</v>
+        <v>-4.8158</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.78</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2977</v>
+        <v>-0.2288</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.5494</v>
+        <v>-5.0336</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.67</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4928</v>
+        <v>-0.331</v>
       </c>
       <c r="J45" t="n">
-        <v>-10.8416</v>
+        <v>-7.282</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.64</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5365</v>
+        <v>-0.3591</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.803</v>
+        <v>-7.9002</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.69</v>
       </c>
       <c r="I47" t="n">
-        <v>1.4704</v>
+        <v>1.0468</v>
       </c>
       <c r="J47" t="n">
-        <v>32.3488</v>
+        <v>23.0296</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.65</v>
       </c>
       <c r="I48" t="n">
-        <v>1.3954</v>
+        <v>1.0002</v>
       </c>
       <c r="J48" t="n">
-        <v>30.6988</v>
+        <v>22.0044</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.48</v>
       </c>
       <c r="I49" t="n">
-        <v>1.0482</v>
+        <v>0.8002</v>
       </c>
       <c r="J49" t="n">
-        <v>23.0604</v>
+        <v>17.6044</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.3</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6273</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>13.8006</v>
+        <v>12.6742</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.16</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3024</v>
+        <v>0.3771</v>
       </c>
       <c r="J51" t="n">
-        <v>6.6528</v>
+        <v>8.296200000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.18</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4275</v>
+        <v>0.4237</v>
       </c>
       <c r="J52" t="n">
-        <v>10.26</v>
+        <v>10.1688</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.9</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.124</v>
+        <v>-0.1123</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.976</v>
+        <v>-2.6952</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.88</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1592</v>
+        <v>-0.1348</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.8208</v>
+        <v>-3.2352</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.6</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6092</v>
+        <v>-0.4056</v>
       </c>
       <c r="J55" t="n">
-        <v>-14.6208</v>
+        <v>-9.734400000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.47</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7721</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>-18.5304</v>
+        <v>-12.6168</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.82</v>
       </c>
       <c r="I57" t="n">
-        <v>1.7594</v>
+        <v>1.2476</v>
       </c>
       <c r="J57" t="n">
-        <v>42.2256</v>
+        <v>29.9424</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.8</v>
       </c>
       <c r="I58" t="n">
-        <v>1.7368</v>
+        <v>1.2236</v>
       </c>
       <c r="J58" t="n">
-        <v>41.6832</v>
+        <v>29.3664</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.96</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3127</v>
+        <v>-0.2303</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.5048</v>
+        <v>-5.5272</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.91</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4637</v>
+        <v>-0.3874</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.1288</v>
+        <v>-9.297599999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.78</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7887</v>
+        <v>-0.7386</v>
       </c>
       <c r="J61" t="n">
-        <v>-18.9288</v>
+        <v>-17.7264</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.43</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0831</v>
+        <v>1.0524</v>
       </c>
       <c r="J62" t="n">
-        <v>27.0775</v>
+        <v>26.31</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.2</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5391</v>
+        <v>0.5611</v>
       </c>
       <c r="J63" t="n">
-        <v>13.4775</v>
+        <v>14.0275</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.15</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3831</v>
+        <v>0.4387</v>
       </c>
       <c r="J64" t="n">
-        <v>9.577500000000001</v>
+        <v>10.9675</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.09</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2108</v>
+        <v>0.2759</v>
       </c>
       <c r="J65" t="n">
-        <v>5.27</v>
+        <v>6.8975</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.09</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2108</v>
+        <v>0.2759</v>
       </c>
       <c r="J66" t="n">
-        <v>5.27</v>
+        <v>6.8975</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.59</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8768</v>
+        <v>1.0699</v>
       </c>
       <c r="J67" t="n">
-        <v>21.92</v>
+        <v>26.7475</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.89</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2335</v>
+        <v>-0.1415</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.8375</v>
+        <v>-3.5375</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.87</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2671</v>
+        <v>-0.163</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.6775</v>
+        <v>-4.075</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.77</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4184</v>
+        <v>-0.2647</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.46</v>
+        <v>-6.6175</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.71</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.3228</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.5125</v>
+        <v>-8.07</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.66</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4959</v>
+        <v>1.3232</v>
       </c>
       <c r="J72" t="n">
-        <v>38.8934</v>
+        <v>34.4032</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.31</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7709</v>
+        <v>0.7991</v>
       </c>
       <c r="J73" t="n">
-        <v>20.0434</v>
+        <v>20.7766</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.18</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4187</v>
+        <v>0.498</v>
       </c>
       <c r="J74" t="n">
-        <v>10.8862</v>
+        <v>12.948</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.16</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3668</v>
+        <v>0.4472</v>
       </c>
       <c r="J75" t="n">
-        <v>9.536799999999999</v>
+        <v>11.6272</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.05</v>
       </c>
       <c r="I76" t="n">
-        <v>0.0562</v>
+        <v>0.1348</v>
       </c>
       <c r="J76" t="n">
-        <v>1.4612</v>
+        <v>3.5048</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.25</v>
       </c>
       <c r="I77" t="n">
-        <v>0.502</v>
+        <v>0.588</v>
       </c>
       <c r="J77" t="n">
-        <v>13.052</v>
+        <v>15.288</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.9</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1538</v>
+        <v>-0.1212</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.9988</v>
+        <v>-3.1512</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.87</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2129</v>
+        <v>-0.1529</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.5354</v>
+        <v>-3.9754</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.71</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4766</v>
+        <v>-0.3101</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.3916</v>
+        <v>-8.0626</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.6</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6228</v>
+        <v>-0.4137</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.1928</v>
+        <v>-10.7562</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.82</v>
       </c>
       <c r="I82" t="n">
-        <v>1.7087</v>
+        <v>1.4721</v>
       </c>
       <c r="J82" t="n">
-        <v>35.8827</v>
+        <v>30.9141</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.8</v>
       </c>
       <c r="I83" t="n">
-        <v>1.6736</v>
+        <v>1.4492</v>
       </c>
       <c r="J83" t="n">
-        <v>35.1456</v>
+        <v>30.4332</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.49</v>
       </c>
       <c r="I84" t="n">
-        <v>1.0773</v>
+        <v>1.0867</v>
       </c>
       <c r="J84" t="n">
-        <v>22.6233</v>
+        <v>22.8207</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.25</v>
       </c>
       <c r="I85" t="n">
-        <v>0.518</v>
+        <v>0.6312</v>
       </c>
       <c r="J85" t="n">
-        <v>10.878</v>
+        <v>13.2552</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.87</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6106</v>
+        <v>-0.5413</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.8226</v>
+        <v>-11.3673</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.8</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.2036</v>
+        <v>-0.1822</v>
       </c>
       <c r="J87" t="n">
-        <v>-4.2756</v>
+        <v>-3.8262</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.71</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.3445</v>
+        <v>-0.2767</v>
       </c>
       <c r="J88" t="n">
-        <v>-7.2345</v>
+        <v>-5.8107</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.71</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3445</v>
+        <v>-0.2767</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.2345</v>
+        <v>-5.8107</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.61</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.526</v>
+        <v>-0.369</v>
       </c>
       <c r="J90" t="n">
-        <v>-11.046</v>
+        <v>-7.749</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.33</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.9101</v>
+        <v>-0.6321</v>
       </c>
       <c r="J91" t="n">
-        <v>-19.1121</v>
+        <v>-13.2741</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.36</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9585</v>
+        <v>0.9474</v>
       </c>
       <c r="J92" t="n">
-        <v>27.7965</v>
+        <v>27.4746</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.12</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3296</v>
+        <v>0.3697</v>
       </c>
       <c r="J93" t="n">
-        <v>9.558400000000001</v>
+        <v>10.7213</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2988</v>
+        <v>0.3428</v>
       </c>
       <c r="J94" t="n">
-        <v>8.6652</v>
+        <v>9.9412</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.08</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2064</v>
+        <v>0.2581</v>
       </c>
       <c r="J95" t="n">
-        <v>5.9856</v>
+        <v>7.4849</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.05</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1096</v>
+        <v>0.1661</v>
       </c>
       <c r="J96" t="n">
-        <v>3.1784</v>
+        <v>4.8169</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.06</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1806</v>
+        <v>0.1773</v>
       </c>
       <c r="J97" t="n">
-        <v>5.2374</v>
+        <v>5.1417</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.03</v>
       </c>
       <c r="I98" t="n">
-        <v>0.12</v>
+        <v>0.1055</v>
       </c>
       <c r="J98" t="n">
-        <v>3.48</v>
+        <v>3.0595</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.97</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.049</v>
+        <v>-0.0452</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.421</v>
+        <v>-1.3108</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.91</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1856</v>
+        <v>-0.1166</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.3824</v>
+        <v>-3.3814</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.72</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4811</v>
+        <v>-0.3098</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.9519</v>
+        <v>-8.9842</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.32</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8629</v>
+        <v>0.8534</v>
       </c>
       <c r="J102" t="n">
-        <v>21.5725</v>
+        <v>21.335</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.19</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5421</v>
+        <v>0.5435</v>
       </c>
       <c r="J103" t="n">
-        <v>13.5525</v>
+        <v>13.5875</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.14</v>
       </c>
       <c r="I104" t="n">
-        <v>0.3812</v>
+        <v>0.4198</v>
       </c>
       <c r="J104" t="n">
-        <v>9.529999999999999</v>
+        <v>10.495</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.11</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2905</v>
+        <v>0.3403</v>
       </c>
       <c r="J105" t="n">
-        <v>7.2625</v>
+        <v>8.5075</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.02</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.0044</v>
+        <v>0.0585</v>
       </c>
       <c r="J106" t="n">
-        <v>-0.11</v>
+        <v>1.4625</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.04</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1598</v>
+        <v>0.1444</v>
       </c>
       <c r="J107" t="n">
-        <v>3.995</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.96</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0487</v>
+        <v>-0.053</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.2175</v>
+        <v>-1.325</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.86</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2544</v>
+        <v>-0.1652</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.36</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.83</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3054</v>
+        <v>-0.1958</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.635</v>
+        <v>-4.895</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.77</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3982</v>
+        <v>-0.2555</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.955</v>
+        <v>-6.3875</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.34</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9003</v>
+        <v>0.8946</v>
       </c>
       <c r="J112" t="n">
-        <v>24.3081</v>
+        <v>24.1542</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.25</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6892</v>
+        <v>0.6849</v>
       </c>
       <c r="J113" t="n">
-        <v>18.6084</v>
+        <v>18.4923</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.14</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3697</v>
+        <v>0.4173</v>
       </c>
       <c r="J114" t="n">
-        <v>9.9819</v>
+        <v>11.2671</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.06</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1293</v>
+        <v>0.1915</v>
       </c>
       <c r="J115" t="n">
-        <v>3.4911</v>
+        <v>5.1705</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.06</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1293</v>
+        <v>0.1915</v>
       </c>
       <c r="J116" t="n">
-        <v>3.4911</v>
+        <v>5.1705</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.27</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5198</v>
+        <v>0.6125</v>
       </c>
       <c r="J117" t="n">
-        <v>14.0346</v>
+        <v>16.5375</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.92</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1285</v>
+        <v>-0.1016</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.4695</v>
+        <v>-2.7432</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.86</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2534</v>
+        <v>-0.165</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.8418</v>
+        <v>-4.455</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3523</v>
+        <v>-0.2256</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.5121</v>
+        <v>-6.0912</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.6</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6276</v>
+        <v>-0.4168</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.9452</v>
+        <v>-11.2536</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.31</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4796</v>
+        <v>0.4158</v>
       </c>
       <c r="J122" t="n">
-        <v>14.388</v>
+        <v>12.474</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.26</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4117</v>
+        <v>0.3569</v>
       </c>
       <c r="J123" t="n">
-        <v>12.351</v>
+        <v>10.707</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.25</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3975</v>
+        <v>0.345</v>
       </c>
       <c r="J124" t="n">
-        <v>11.925</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.15</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2316</v>
+        <v>0.2231</v>
       </c>
       <c r="J125" t="n">
-        <v>6.948</v>
+        <v>6.693</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3292</v>
+        <v>-0.1953</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.875999999999999</v>
+        <v>-5.859</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.47</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7464</v>
+        <v>0.7116</v>
       </c>
       <c r="J127" t="n">
-        <v>22.392</v>
+        <v>21.348</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.16</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3424</v>
+        <v>0.2909</v>
       </c>
       <c r="J128" t="n">
-        <v>10.272</v>
+        <v>8.727</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.08</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2124</v>
+        <v>0.1668</v>
       </c>
       <c r="J129" t="n">
-        <v>6.372</v>
+        <v>5.004</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.6</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.6382</v>
+        <v>-0.4238</v>
       </c>
       <c r="J130" t="n">
-        <v>-19.146</v>
+        <v>-12.714</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.44</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8266</v>
+        <v>-0.5682</v>
       </c>
       <c r="J131" t="n">
-        <v>-24.798</v>
+        <v>-17.046</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.33</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5522</v>
+        <v>0.6612</v>
       </c>
       <c r="J132" t="n">
-        <v>13.805</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.16</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3172</v>
+        <v>0.3584</v>
       </c>
       <c r="J133" t="n">
-        <v>7.93</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2025</v>
+        <v>0.2213</v>
       </c>
       <c r="J134" t="n">
-        <v>5.0625</v>
+        <v>5.5325</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.85</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3142</v>
+        <v>-0.1902</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.855</v>
+        <v>-4.755</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.67</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5622</v>
+        <v>-0.3667</v>
       </c>
       <c r="J136" t="n">
-        <v>-14.055</v>
+        <v>-9.1675</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.48</v>
       </c>
       <c r="I137" t="n">
-        <v>1.23</v>
+        <v>1.1412</v>
       </c>
       <c r="J137" t="n">
-        <v>30.75</v>
+        <v>28.53</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3006</v>
+        <v>0.3224</v>
       </c>
       <c r="J138" t="n">
-        <v>7.515</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.03</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0594</v>
+        <v>0.108</v>
       </c>
       <c r="J139" t="n">
-        <v>1.485</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.99</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1424</v>
+        <v>-0.0793</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.56</v>
+        <v>-1.9825</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.93</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3565</v>
+        <v>-0.2893</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.9125</v>
+        <v>-7.2325</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.5</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7269</v>
+        <v>0.9032</v>
       </c>
       <c r="J142" t="n">
-        <v>21.0801</v>
+        <v>26.1928</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.2</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3428</v>
+        <v>0.4084</v>
       </c>
       <c r="J143" t="n">
-        <v>9.9412</v>
+        <v>11.8436</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1104</v>
+        <v>0.1658</v>
       </c>
       <c r="J144" t="n">
-        <v>3.2016</v>
+        <v>4.8082</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.06</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0914</v>
+        <v>0.1444</v>
       </c>
       <c r="J145" t="n">
-        <v>2.6506</v>
+        <v>4.1876</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.75</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4741</v>
+        <v>-0.3007</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.7489</v>
+        <v>-8.7203</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.27</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8141</v>
+        <v>0.7809</v>
       </c>
       <c r="J147" t="n">
-        <v>23.6089</v>
+        <v>22.6461</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.27</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8141</v>
+        <v>0.7809</v>
       </c>
       <c r="J148" t="n">
-        <v>23.6089</v>
+        <v>22.6461</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.99</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1031</v>
+        <v>-0.0618</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.9899</v>
+        <v>-1.7922</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.95</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2595</v>
+        <v>-0.2073</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.5255</v>
+        <v>-6.0117</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.71</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8942</v>
+        <v>-0.86</v>
       </c>
       <c r="J151" t="n">
-        <v>-25.9318</v>
+        <v>-24.94</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.87</v>
       </c>
       <c r="I152" t="n">
-        <v>1.8317</v>
+        <v>1.5503</v>
       </c>
       <c r="J152" t="n">
-        <v>43.9608</v>
+        <v>37.2072</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.56</v>
       </c>
       <c r="I153" t="n">
-        <v>1.2658</v>
+        <v>1.1833</v>
       </c>
       <c r="J153" t="n">
-        <v>30.3792</v>
+        <v>28.3992</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.25</v>
       </c>
       <c r="I154" t="n">
-        <v>0.5518</v>
+        <v>0.6494</v>
       </c>
       <c r="J154" t="n">
-        <v>13.2432</v>
+        <v>15.5856</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.17</v>
       </c>
       <c r="I155" t="n">
-        <v>0.3577</v>
+        <v>0.4538</v>
       </c>
       <c r="J155" t="n">
-        <v>8.5848</v>
+        <v>10.8912</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4027</v>
+        <v>-0.3194</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.6648</v>
+        <v>-7.6656</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.3</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5854</v>
+        <v>0.7066</v>
       </c>
       <c r="J157" t="n">
-        <v>14.0496</v>
+        <v>16.9584</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0847</v>
+        <v>0.0467</v>
       </c>
       <c r="J158" t="n">
-        <v>2.0328</v>
+        <v>1.1208</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.72</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.4491</v>
+        <v>-0.2948</v>
       </c>
       <c r="J159" t="n">
-        <v>-10.7784</v>
+        <v>-7.0752</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.67</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.52</v>
+        <v>-0.3424</v>
       </c>
       <c r="J160" t="n">
-        <v>-12.48</v>
+        <v>-8.217599999999999</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.43</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.8224</v>
+        <v>-0.5644</v>
       </c>
       <c r="J161" t="n">
-        <v>-19.7376</v>
+        <v>-13.5456</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>2.41</v>
       </c>
       <c r="I162" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J162" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.84</v>
       </c>
       <c r="I163" t="n">
-        <v>1.6297</v>
+        <v>1.4509</v>
       </c>
       <c r="J163" t="n">
-        <v>27.7049</v>
+        <v>24.6653</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.73</v>
       </c>
       <c r="I164" t="n">
-        <v>1.4094</v>
+        <v>1.3335</v>
       </c>
       <c r="J164" t="n">
-        <v>23.9598</v>
+        <v>22.6695</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.43</v>
       </c>
       <c r="I165" t="n">
-        <v>0.8158</v>
+        <v>0.9715</v>
       </c>
       <c r="J165" t="n">
-        <v>13.8686</v>
+        <v>16.5155</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.24</v>
       </c>
       <c r="I166" t="n">
-        <v>0.4246</v>
+        <v>0.5536</v>
       </c>
       <c r="J166" t="n">
-        <v>7.2182</v>
+        <v>9.411199999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.58</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.3479</v>
+        <v>-0.2912</v>
       </c>
       <c r="J167" t="n">
-        <v>-5.9143</v>
+        <v>-4.9504</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.35</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.7553</v>
+        <v>-0.5507</v>
       </c>
       <c r="J168" t="n">
-        <v>-12.8401</v>
+        <v>-9.3619</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.32</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.5797</v>
       </c>
       <c r="J169" t="n">
-        <v>-13.889</v>
+        <v>-9.854900000000001</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.31</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.8351</v>
+        <v>-0.5899</v>
       </c>
       <c r="J170" t="n">
-        <v>-14.1967</v>
+        <v>-10.0283</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.22</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.9806</v>
+        <v>-0.6876</v>
       </c>
       <c r="J171" t="n">
-        <v>-16.6702</v>
+        <v>-11.6892</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.77</v>
       </c>
       <c r="I172" t="n">
-        <v>1.598</v>
+        <v>1.4049</v>
       </c>
       <c r="J172" t="n">
-        <v>31.96</v>
+        <v>28.098</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.72</v>
       </c>
       <c r="I173" t="n">
-        <v>1.5072</v>
+        <v>1.3479</v>
       </c>
       <c r="J173" t="n">
-        <v>30.144</v>
+        <v>26.958</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.68</v>
       </c>
       <c r="I174" t="n">
-        <v>1.4328</v>
+        <v>1.302</v>
       </c>
       <c r="J174" t="n">
-        <v>28.656</v>
+        <v>26.04</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.37</v>
       </c>
       <c r="I175" t="n">
-        <v>0.7639</v>
+        <v>0.8914</v>
       </c>
       <c r="J175" t="n">
-        <v>15.278</v>
+        <v>17.828</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.96</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3697</v>
+        <v>-0.2825</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.394</v>
+        <v>-5.65</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I177" t="n">
-        <v>0.0508</v>
+        <v>0.0065</v>
       </c>
       <c r="J177" t="n">
-        <v>1.016</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.73</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2936</v>
+        <v>-0.2471</v>
       </c>
       <c r="J178" t="n">
-        <v>-5.872</v>
+        <v>-4.942</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.57</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.5702</v>
+        <v>-0.3997</v>
       </c>
       <c r="J179" t="n">
-        <v>-11.404</v>
+        <v>-7.994</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.48</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.706</v>
+        <v>-0.4834</v>
       </c>
       <c r="J180" t="n">
-        <v>-14.12</v>
+        <v>-9.667999999999999</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.27</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.977</v>
+        <v>-0.6847</v>
       </c>
       <c r="J181" t="n">
-        <v>-19.54</v>
+        <v>-13.694</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.72</v>
       </c>
       <c r="I182" t="n">
-        <v>1.5807</v>
+        <v>1.3817</v>
       </c>
       <c r="J182" t="n">
-        <v>34.7754</v>
+        <v>30.3974</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.39</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9246</v>
+        <v>0.958</v>
       </c>
       <c r="J183" t="n">
-        <v>20.3412</v>
+        <v>21.076</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.2</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4437</v>
+        <v>0.5355</v>
       </c>
       <c r="J184" t="n">
-        <v>9.7614</v>
+        <v>11.781</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.17</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3689</v>
+        <v>0.4604</v>
       </c>
       <c r="J185" t="n">
-        <v>8.1158</v>
+        <v>10.1288</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.16</v>
       </c>
       <c r="I186" t="n">
-        <v>0.3436</v>
+        <v>0.4347</v>
       </c>
       <c r="J186" t="n">
-        <v>7.5592</v>
+        <v>9.5634</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1</v>
       </c>
       <c r="I187" t="n">
-        <v>0.1258</v>
+        <v>0.0924</v>
       </c>
       <c r="J187" t="n">
-        <v>2.7676</v>
+        <v>2.0328</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.76</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.3219</v>
+        <v>-0.2459</v>
       </c>
       <c r="J188" t="n">
-        <v>-7.0818</v>
+        <v>-5.4098</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.64</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.5304</v>
+        <v>-0.3566</v>
       </c>
       <c r="J189" t="n">
-        <v>-11.6688</v>
+        <v>-7.8452</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.64</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5304</v>
+        <v>-0.3566</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.6688</v>
+        <v>-7.8452</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.61</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5732</v>
+        <v>-0.3847</v>
       </c>
       <c r="J191" t="n">
-        <v>-12.6104</v>
+        <v>-8.4634</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.11</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2917</v>
+        <v>0.3078</v>
       </c>
       <c r="J192" t="n">
-        <v>8.750999999999999</v>
+        <v>9.234</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1</v>
       </c>
       <c r="I193" t="n">
-        <v>0.063</v>
+        <v>0.028</v>
       </c>
       <c r="J193" t="n">
-        <v>1.89</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.91</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1402</v>
+        <v>-0.1113</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.206</v>
+        <v>-3.339</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.68</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.5204</v>
+        <v>-0.34</v>
       </c>
       <c r="J195" t="n">
-        <v>-15.612</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.68</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5204</v>
+        <v>-0.34</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.612</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.42</v>
       </c>
       <c r="I197" t="n">
-        <v>1.057</v>
+        <v>1.0359</v>
       </c>
       <c r="J197" t="n">
-        <v>31.71</v>
+        <v>31.077</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.21</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5589</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="J198" t="n">
-        <v>16.767</v>
+        <v>17.496</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.2</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5224</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J199" t="n">
-        <v>15.672</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.19</v>
       </c>
       <c r="I200" t="n">
-        <v>0.4904</v>
+        <v>0.5363</v>
       </c>
       <c r="J200" t="n">
-        <v>14.712</v>
+        <v>16.089</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.99</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1825</v>
+        <v>-0.1041</v>
       </c>
       <c r="J201" t="n">
-        <v>-5.475</v>
+        <v>-3.123</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.5</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2402</v>
+        <v>1.1507</v>
       </c>
       <c r="J202" t="n">
-        <v>35.9658</v>
+        <v>33.3703</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.3</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8125</v>
+        <v>0.8042</v>
       </c>
       <c r="J203" t="n">
-        <v>23.5625</v>
+        <v>23.3218</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.03</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0301</v>
+        <v>0.0935</v>
       </c>
       <c r="J204" t="n">
-        <v>0.8729</v>
+        <v>2.7115</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.02</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.008</v>
+        <v>0.0564</v>
       </c>
       <c r="J205" t="n">
-        <v>-0.232</v>
+        <v>1.6356</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.97</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2479</v>
+        <v>-0.1728</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.1891</v>
+        <v>-5.0112</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.23</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4662</v>
+        <v>0.5392</v>
       </c>
       <c r="J207" t="n">
-        <v>13.5198</v>
+        <v>15.6368</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.9</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1672</v>
+        <v>-0.1235</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.8488</v>
+        <v>-3.5815</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.84</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2871</v>
+        <v>-0.1852</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.325900000000001</v>
+        <v>-5.3708</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.78</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.382</v>
+        <v>-0.2452</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.078</v>
+        <v>-7.1108</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5099</v>
+        <v>-0.3321</v>
       </c>
       <c r="J211" t="n">
-        <v>-14.7871</v>
+        <v>-9.6309</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3460/event_3460_evp_summary.xlsx
+++ b/database/event/3460/event_3460_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7174</v>
+        <v>5.8351</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9638</v>
+        <v>2.0042</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9431</v>
+        <v>2.0321</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7174</v>
+        <v>5.8351</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6118</v>
+        <v>2.5172</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1056</v>
+        <v>3.3179</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7159</v>
+        <v>3.411</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9321</v>
+        <v>1.8419</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1056</v>
+        <v>3.3179</v>
       </c>
       <c r="K2" t="n">
         <v>102</v>
@@ -529,7 +529,7 @@
         <v>103</v>
       </c>
       <c r="M2" t="n">
-        <v>5.0377</v>
+        <v>5.1598</v>
       </c>
       <c r="N2" t="n">
         <v>205</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5333</v>
+        <v>5.621</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9005</v>
+        <v>1.9307</v>
       </c>
       <c r="D3" t="n">
-        <v>1.86</v>
+        <v>1.9346</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5333</v>
+        <v>5.621</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6715</v>
+        <v>2.6073</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8618</v>
+        <v>3.0137</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9263</v>
+        <v>3.7084</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0415</v>
+        <v>2.0025</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8618</v>
+        <v>3.0137</v>
       </c>
       <c r="K3" t="n">
         <v>102</v>
@@ -575,7 +575,7 @@
         <v>103</v>
       </c>
       <c r="M3" t="n">
-        <v>4.9033</v>
+        <v>5.0162</v>
       </c>
       <c r="N3" t="n">
         <v>205</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6378</v>
+        <v>4.671</v>
       </c>
       <c r="C4" t="n">
-        <v>1.593</v>
+        <v>1.6044</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4557</v>
+        <v>1.5021</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6378</v>
+        <v>4.671</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7503</v>
+        <v>2.6768</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8875</v>
+        <v>1.9942</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2039</v>
+        <v>3.9375</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1858</v>
+        <v>2.1262</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8875</v>
+        <v>1.9942</v>
       </c>
       <c r="K4" t="n">
         <v>51</v>
@@ -621,7 +621,7 @@
         <v>111</v>
       </c>
       <c r="M4" t="n">
-        <v>4.0733</v>
+        <v>4.1204</v>
       </c>
       <c r="N4" t="n">
         <v>162</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6301</v>
+        <v>3.635</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2468</v>
+        <v>1.2485</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0008</v>
+        <v>1.0305</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6301</v>
+        <v>3.635</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4827</v>
+        <v>2.4269</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1474</v>
+        <v>1.2081</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2611</v>
+        <v>3.1132</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6956</v>
+        <v>1.6811</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1474</v>
+        <v>1.2081</v>
       </c>
       <c r="K5" t="n">
         <v>102</v>
@@ -667,7 +667,7 @@
         <v>103</v>
       </c>
       <c r="M5" t="n">
-        <v>2.843</v>
+        <v>2.8892</v>
       </c>
       <c r="N5" t="n">
         <v>205</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.4609</v>
+        <v>3.4881</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1887</v>
+        <v>1.1981</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9244</v>
+        <v>0.9637</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4609</v>
+        <v>3.4881</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4716</v>
+        <v>2.4038</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9893</v>
+        <v>1.0843</v>
       </c>
       <c r="H6" t="n">
-        <v>3.222</v>
+        <v>3.0369</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6753</v>
+        <v>1.6399</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9893</v>
+        <v>1.0843</v>
       </c>
       <c r="K6" t="n">
         <v>92</v>
@@ -713,7 +713,7 @@
         <v>54</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6646</v>
+        <v>2.7242</v>
       </c>
       <c r="N6" t="n">
         <v>146</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3669</v>
+        <v>3.4814</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1564</v>
+        <v>1.1958</v>
       </c>
       <c r="D7" t="n">
-        <v>0.882</v>
+        <v>0.9606</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3669</v>
+        <v>3.4814</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1841</v>
+        <v>3.2753</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1828</v>
+        <v>0.2061</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7325</v>
+        <v>5.9121</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9806</v>
+        <v>3.1925</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1828</v>
+        <v>0.2061</v>
       </c>
       <c r="K7" t="n">
         <v>92</v>
@@ -759,7 +759,7 @@
         <v>54</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1634</v>
+        <v>3.3986</v>
       </c>
       <c r="N7" t="n">
         <v>146</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2266</v>
+        <v>3.1579</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1083</v>
+        <v>1.0847</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8186</v>
+        <v>0.8133</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2266</v>
+        <v>3.1579</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7082</v>
+        <v>2.6164</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5184</v>
+        <v>0.5415</v>
       </c>
       <c r="H8" t="n">
-        <v>4.0556</v>
+        <v>3.7382</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1087</v>
+        <v>2.0186</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5184</v>
+        <v>0.5415</v>
       </c>
       <c r="K8" t="n">
         <v>51</v>
@@ -805,7 +805,7 @@
         <v>111</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6271</v>
+        <v>2.5601</v>
       </c>
       <c r="N8" t="n">
         <v>162</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7513</v>
+        <v>2.6808</v>
       </c>
       <c r="C9" t="n">
-        <v>0.945</v>
+        <v>0.9208</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6041</v>
+        <v>0.5962</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7513</v>
+        <v>2.6808</v>
       </c>
       <c r="F9" t="n">
-        <v>3.105</v>
+        <v>3.0728</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3537</v>
+        <v>-0.392</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4539</v>
+        <v>5.244</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8358</v>
+        <v>2.8317</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3537</v>
+        <v>-0.392</v>
       </c>
       <c r="K9" t="n">
         <v>44</v>
@@ -851,7 +851,7 @@
         <v>46</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4821</v>
+        <v>2.4397</v>
       </c>
       <c r="N9" t="n">
         <v>90</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6879</v>
+        <v>2.606</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9232</v>
+        <v>0.8951</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5754</v>
+        <v>0.5621</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6879</v>
+        <v>2.606</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0683</v>
+        <v>3.016</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3804</v>
+        <v>-0.41</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3245</v>
+        <v>5.0567</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7685</v>
+        <v>2.7306</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3804</v>
+        <v>-0.41</v>
       </c>
       <c r="K10" t="n">
         <v>92</v>
@@ -897,7 +897,7 @@
         <v>54</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3881</v>
+        <v>2.3206</v>
       </c>
       <c r="N10" t="n">
         <v>146</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5264</v>
+        <v>2.5703</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8678</v>
+        <v>0.8828</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5264</v>
+        <v>2.5703</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9697</v>
+        <v>0.6728</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4433</v>
+        <v>1.8975</v>
       </c>
       <c r="H11" t="n">
-        <v>4.9771</v>
+        <v>0.6728</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5878</v>
+        <v>0.3633</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4433</v>
+        <v>1.8975</v>
       </c>
       <c r="K11" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="L11" t="n">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1445</v>
+        <v>2.2608</v>
       </c>
       <c r="N11" t="n">
-        <v>90</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4805</v>
+        <v>2.4369</v>
       </c>
       <c r="C12" t="n">
-        <v>0.852</v>
+        <v>0.837</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4818</v>
+        <v>0.4851</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4805</v>
+        <v>2.4369</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6976</v>
+        <v>2.9158</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7829</v>
+        <v>-0.4789</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6976</v>
+        <v>4.7262</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3627</v>
+        <v>2.5521</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7829</v>
+        <v>-0.4789</v>
       </c>
       <c r="K12" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="L12" t="n">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1456</v>
+        <v>2.0732</v>
       </c>
       <c r="N12" t="n">
-        <v>162</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4121</v>
+        <v>2.4311</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8285</v>
+        <v>0.835</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4509</v>
+        <v>0.4825</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4121</v>
+        <v>2.4311</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1182</v>
+        <v>0.9922</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2939</v>
+        <v>1.4389</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1182</v>
+        <v>0.9922</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5814</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2939</v>
+        <v>1.4389</v>
       </c>
       <c r="K13" t="n">
         <v>102</v>
@@ -1035,7 +1035,7 @@
         <v>103</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8753</v>
+        <v>1.9747</v>
       </c>
       <c r="N13" t="n">
         <v>205</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.356</v>
+        <v>2.2955</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8092</v>
+        <v>0.7884</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4256</v>
+        <v>0.4208</v>
       </c>
       <c r="E14" t="n">
-        <v>2.356</v>
+        <v>2.2955</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2914</v>
+        <v>2.2164</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0646</v>
+        <v>0.0791</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5872</v>
+        <v>2.4186</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3452</v>
+        <v>1.306</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0646</v>
+        <v>0.0791</v>
       </c>
       <c r="K14" t="n">
         <v>44</v>
@@ -1081,7 +1081,7 @@
         <v>46</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4098</v>
+        <v>1.3851</v>
       </c>
       <c r="N14" t="n">
         <v>90</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.201</v>
+        <v>2.1657</v>
       </c>
       <c r="C15" t="n">
-        <v>0.756</v>
+        <v>0.7439</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3556</v>
+        <v>0.3617</v>
       </c>
       <c r="E15" t="n">
-        <v>2.201</v>
+        <v>2.1657</v>
       </c>
       <c r="F15" t="n">
-        <v>2.201</v>
+        <v>1.0146</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1.1511</v>
       </c>
       <c r="H15" t="n">
-        <v>2.201</v>
+        <v>1.0146</v>
       </c>
       <c r="I15" t="n">
-        <v>2.201</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1.1511</v>
       </c>
       <c r="K15" t="n">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="M15" t="n">
-        <v>2.201</v>
+        <v>1.699</v>
       </c>
       <c r="N15" t="n">
-        <v>123</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0869</v>
+        <v>2.0355</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7168</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3041</v>
+        <v>0.3024</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0869</v>
+        <v>2.0355</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0159</v>
+        <v>2.0355</v>
       </c>
       <c r="G16" t="n">
-        <v>1.071</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0159</v>
+        <v>2.0355</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5282</v>
+        <v>2.0355</v>
       </c>
       <c r="J16" t="n">
-        <v>1.071</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="L16" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5992</v>
+        <v>2.0355</v>
       </c>
       <c r="N16" t="n">
-        <v>162</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0286</v>
+        <v>1.9332</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6968</v>
+        <v>0.664</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2778</v>
+        <v>0.2558</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0286</v>
+        <v>1.9332</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9444</v>
+        <v>2.8658</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.9326</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8879</v>
+        <v>4.5612</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5415</v>
+        <v>2.463</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.9326</v>
       </c>
       <c r="K17" t="n">
         <v>92</v>
@@ -1219,7 +1219,7 @@
         <v>54</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6257</v>
+        <v>1.5304</v>
       </c>
       <c r="N17" t="n">
         <v>146</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9437</v>
+        <v>1.8394</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6676</v>
+        <v>0.6318</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2395</v>
+        <v>0.2131</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9437</v>
+        <v>1.8394</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3212</v>
+        <v>2.2419</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3775</v>
+        <v>-0.4025</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6922</v>
+        <v>2.5026</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3998</v>
+        <v>1.3514</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3775</v>
+        <v>-0.4025</v>
       </c>
       <c r="K18" t="n">
         <v>92</v>
@@ -1265,7 +1265,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0223</v>
+        <v>0.9488999999999999</v>
       </c>
       <c r="N18" t="n">
         <v>146</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4785</v>
+        <v>1.4126</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5078</v>
+        <v>0.4852</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0295</v>
+        <v>0.0188</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4785</v>
+        <v>1.4126</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4785</v>
+        <v>1.4126</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4785</v>
+        <v>1.4126</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4785</v>
+        <v>1.4126</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4785</v>
+        <v>1.4126</v>
       </c>
       <c r="N19" t="n">
         <v>164</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4159</v>
+        <v>1.3345</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4863</v>
+        <v>0.4584</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0012</v>
+        <v>-0.0167</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4159</v>
+        <v>1.3345</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9781</v>
+        <v>1.9304</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5622</v>
+        <v>-0.5959</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9781</v>
+        <v>1.9304</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0285</v>
+        <v>1.0424</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5622</v>
+        <v>-0.5959</v>
       </c>
       <c r="K20" t="n">
         <v>44</v>
@@ -1357,7 +1357,7 @@
         <v>46</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4662999999999999</v>
+        <v>0.4465</v>
       </c>
       <c r="N20" t="n">
         <v>90</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1945</v>
+        <v>1.198</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4103</v>
+        <v>0.4115</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0988</v>
+        <v>-0.0788</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1945</v>
+        <v>1.198</v>
       </c>
       <c r="F21" t="n">
-        <v>2.262</v>
+        <v>2.1824</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0675</v>
+        <v>-0.9844000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4835</v>
+        <v>2.3065</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2913</v>
+        <v>1.2455</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0675</v>
+        <v>-0.9844000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>102</v>
@@ -1403,7 +1403,7 @@
         <v>103</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2238</v>
+        <v>0.2611</v>
       </c>
       <c r="N21" t="n">
         <v>205</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0591</v>
+        <v>1.0611</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3638</v>
+        <v>0.3645</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1599</v>
+        <v>-0.1412</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0591</v>
+        <v>1.0611</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0591</v>
+        <v>1.0611</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0591</v>
+        <v>1.0611</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0591</v>
+        <v>1.0611</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0591</v>
+        <v>1.0611</v>
       </c>
       <c r="N22" t="n">
         <v>113</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8185</v>
+        <v>0.8102</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2811</v>
+        <v>0.2783</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2685</v>
+        <v>-0.2554</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8185</v>
+        <v>0.8102</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8185</v>
+        <v>0.8102</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8185</v>
+        <v>0.8102</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8185</v>
+        <v>0.8102</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8185</v>
+        <v>0.8102</v>
       </c>
       <c r="N23" t="n">
         <v>113</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7509</v>
+        <v>0.697</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2579</v>
+        <v>0.2394</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.299</v>
+        <v>-0.3069</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7509</v>
+        <v>0.697</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7509</v>
+        <v>0.697</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7509</v>
+        <v>0.697</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7509</v>
+        <v>0.697</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7509</v>
+        <v>0.697</v>
       </c>
       <c r="N24" t="n">
         <v>113</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.5851</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2187</v>
+        <v>0.201</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3506</v>
+        <v>-0.3579</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.5851</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.5851</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.5851</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.5851</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.5851</v>
       </c>
       <c r="N25" t="n">
         <v>123</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4988</v>
+        <v>0.5185</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1713</v>
+        <v>0.1781</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4128</v>
+        <v>-0.3882</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4988</v>
+        <v>0.5185</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4988</v>
+        <v>0.5185</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4988</v>
+        <v>0.5185</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4988</v>
+        <v>0.5185</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4988</v>
+        <v>0.5185</v>
       </c>
       <c r="N26" t="n">
         <v>113</v>
@@ -1642,78 +1642,78 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3339</v>
+        <v>0.2588</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1147</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4873</v>
+        <v>-0.5064</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3339</v>
+        <v>0.2588</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3339</v>
+        <v>0.9902</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3339</v>
+        <v>0.9902</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3339</v>
+        <v>0.5347</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3339</v>
+        <v>-0.1967000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>123</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2697</v>
+        <v>0.237</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0926</v>
+        <v>0.0814</v>
       </c>
       <c r="D28" t="n">
         <v>-0.5163</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2697</v>
+        <v>0.237</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2697</v>
+        <v>0.237</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2697</v>
+        <v>0.237</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2697</v>
+        <v>0.237</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2697</v>
+        <v>0.237</v>
       </c>
       <c r="N28" t="n">
         <v>123</v>
@@ -1734,185 +1734,185 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.237</v>
+        <v>0.1973</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0814</v>
+        <v>0.0678</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.531</v>
+        <v>-0.5344</v>
       </c>
       <c r="E29" t="n">
-        <v>0.237</v>
+        <v>0.1973</v>
       </c>
       <c r="F29" t="n">
-        <v>0.237</v>
+        <v>0.1973</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.237</v>
+        <v>0.1973</v>
       </c>
       <c r="I29" t="n">
-        <v>0.237</v>
+        <v>0.1973</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.237</v>
+        <v>0.1973</v>
       </c>
       <c r="N29" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.199</v>
+        <v>0.1758</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0684</v>
+        <v>0.0604</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5482</v>
+        <v>-0.5442</v>
       </c>
       <c r="E30" t="n">
-        <v>0.199</v>
+        <v>0.1758</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9939</v>
+        <v>0.1758</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.7949000000000001</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9939</v>
+        <v>0.1758</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5168</v>
+        <v>0.1758</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.7949000000000001</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>51</v>
+        <v>164</v>
       </c>
       <c r="L30" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2781</v>
+        <v>0.1758</v>
       </c>
       <c r="N30" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>NEKIZ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1206</v>
+        <v>0.0393</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0414</v>
+        <v>0.0135</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5836</v>
+        <v>-0.6063</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1206</v>
+        <v>0.0393</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1206</v>
+        <v>0.0393</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1206</v>
+        <v>0.0393</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1206</v>
+        <v>0.0393</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>164</v>
+        <v>69</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1206</v>
+        <v>0.0393</v>
       </c>
       <c r="N31" t="n">
-        <v>164</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NEKIZ</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0693</v>
+        <v>0.0375</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0238</v>
+        <v>0.0129</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6067</v>
+        <v>-0.6071</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0693</v>
+        <v>0.0375</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0693</v>
+        <v>0.0375</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0693</v>
+        <v>0.0375</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0693</v>
+        <v>0.0375</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0693</v>
+        <v>0.0375</v>
       </c>
       <c r="N32" t="n">
-        <v>69</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0489</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0168</v>
+        <v>-0.0266</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6601</v>
+        <v>-0.6594</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.0489</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7056</v>
+        <v>0.7035</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-0.7808</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7056</v>
+        <v>0.7035</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3669</v>
+        <v>0.3799</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-0.7808</v>
       </c>
       <c r="K33" t="n">
         <v>44</v>
@@ -1955,7 +1955,7 @@
         <v>46</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3875999999999999</v>
+        <v>-0.4009</v>
       </c>
       <c r="N33" t="n">
         <v>90</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3235</v>
+        <v>-0.3742</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1111</v>
+        <v>-0.1285</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7841</v>
+        <v>-0.7945</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3235</v>
+        <v>-0.3742</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3235</v>
+        <v>-0.3742</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3235</v>
+        <v>-0.3742</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3235</v>
+        <v>-0.3742</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3235</v>
+        <v>-0.3742</v>
       </c>
       <c r="N34" t="n">
         <v>113</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7117</v>
+        <v>-0.7849</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2445</v>
+        <v>-0.2696</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9593</v>
+        <v>-0.9815</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7117</v>
+        <v>-0.7849</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7117</v>
+        <v>-0.7849</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7117</v>
+        <v>-0.7849</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7117</v>
+        <v>-0.7849</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7117</v>
+        <v>-0.7849</v>
       </c>
       <c r="N35" t="n">
         <v>69</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7934</v>
+        <v>-0.8209</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2725</v>
+        <v>-0.282</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9962</v>
+        <v>-0.9979</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7934</v>
+        <v>-0.8209</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7934</v>
+        <v>-0.8209</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7934</v>
+        <v>-0.8209</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7934</v>
+        <v>-0.8209</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7934</v>
+        <v>-0.8209</v>
       </c>
       <c r="N36" t="n">
         <v>164</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8293</v>
+        <v>-0.8744</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2848</v>
+        <v>-0.3003</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0124</v>
+        <v>-1.0222</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8293</v>
+        <v>-0.8744</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8293</v>
+        <v>-0.8744</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8293</v>
+        <v>-0.8744</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8293</v>
+        <v>-0.8744</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8293</v>
+        <v>-0.8744</v>
       </c>
       <c r="N37" t="n">
         <v>69</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8771</v>
+        <v>-0.8832</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3013</v>
+        <v>-0.3034</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.034</v>
+        <v>-1.0263</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8771</v>
+        <v>-0.8832</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8771</v>
+        <v>-0.8832</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8771</v>
+        <v>-0.8832</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8771</v>
+        <v>-0.8832</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8771</v>
+        <v>-0.8832</v>
       </c>
       <c r="N38" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.8863</v>
+        <v>-0.9222</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3044</v>
+        <v>-0.3168</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0381</v>
+        <v>-1.044</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.8863</v>
+        <v>-0.9222</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.8863</v>
+        <v>-0.9222</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8863</v>
+        <v>-0.9222</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8863</v>
+        <v>-0.9222</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.8863</v>
+        <v>-0.9222</v>
       </c>
       <c r="N39" t="n">
-        <v>123</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1719</v>
+        <v>-1.2121</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4025</v>
+        <v>-0.4163</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1671</v>
+        <v>-1.176</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1719</v>
+        <v>-1.2121</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.1719</v>
+        <v>-1.2121</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.1719</v>
+        <v>-1.2121</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1719</v>
+        <v>-1.2121</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.1719</v>
+        <v>-1.2121</v>
       </c>
       <c r="N40" t="n">
         <v>69</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.6107</v>
+        <v>-1.632</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5532</v>
+        <v>-0.5605</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3652</v>
+        <v>-1.3671</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6107</v>
+        <v>-1.632</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.6107</v>
+        <v>-1.632</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.6107</v>
+        <v>-1.632</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.6107</v>
+        <v>-1.632</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.6107</v>
+        <v>-1.632</v>
       </c>
       <c r="N41" t="n">
         <v>164</v>
@@ -2429,10 +2429,10 @@
         <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8547</v>
+        <v>0.8184</v>
       </c>
       <c r="J2" t="n">
-        <v>25.641</v>
+        <v>24.552</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7428</v>
+        <v>0.7181</v>
       </c>
       <c r="J3" t="n">
-        <v>22.284</v>
+        <v>21.543</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.12</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2637</v>
+        <v>0.2745</v>
       </c>
       <c r="J4" t="n">
-        <v>7.911</v>
+        <v>8.234999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0738</v>
+        <v>0.0872</v>
       </c>
       <c r="J5" t="n">
-        <v>2.214</v>
+        <v>2.616</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.58</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4585</v>
+        <v>-0.4633</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.755</v>
+        <v>-13.899</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8486</v>
+        <v>0.7914</v>
       </c>
       <c r="J7" t="n">
-        <v>25.458</v>
+        <v>23.742</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4965</v>
+        <v>0.48</v>
       </c>
       <c r="J8" t="n">
-        <v>14.895</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.98</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1056</v>
+        <v>-0.1077</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.168</v>
+        <v>-3.231</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.91</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.334</v>
+        <v>-0.325</v>
       </c>
       <c r="J10" t="n">
-        <v>-10.02</v>
+        <v>-9.75</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.9</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3632</v>
+        <v>-0.3519</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.896</v>
+        <v>-10.557</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.55</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9883</v>
+        <v>0.9433</v>
       </c>
       <c r="J12" t="n">
-        <v>26.6841</v>
+        <v>25.4691</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4174</v>
+        <v>0.4182</v>
       </c>
       <c r="J13" t="n">
-        <v>11.2698</v>
+        <v>11.2914</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1504</v>
+        <v>0.1621</v>
       </c>
       <c r="J14" t="n">
-        <v>4.0608</v>
+        <v>4.3767</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.8</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2475</v>
+        <v>-0.2591</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.6825</v>
+        <v>-6.9957</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.77</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2772</v>
+        <v>-0.2884</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.4844</v>
+        <v>-7.7868</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.53</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2049</v>
+        <v>1.2252</v>
       </c>
       <c r="J17" t="n">
-        <v>32.5323</v>
+        <v>33.0804</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.17</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5039</v>
+        <v>0.4905</v>
       </c>
       <c r="J18" t="n">
-        <v>13.6053</v>
+        <v>13.2435</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.02</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0696</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8792</v>
+        <v>2.2437</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2597</v>
+        <v>-0.2517</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.0119</v>
+        <v>-6.7959</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.9</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3805</v>
+        <v>-0.364</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.2735</v>
+        <v>-9.827999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.32</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6733</v>
+        <v>0.7373</v>
       </c>
       <c r="J22" t="n">
-        <v>20.199</v>
+        <v>22.119</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.07</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2529</v>
+        <v>0.2547</v>
       </c>
       <c r="J23" t="n">
-        <v>7.587</v>
+        <v>7.641</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.02</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0895</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>2.685</v>
+        <v>2.901</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.87</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4407</v>
+        <v>-0.4243</v>
       </c>
       <c r="J25" t="n">
-        <v>-13.221</v>
+        <v>-12.729</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.84</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5226</v>
+        <v>-0.4981</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.678</v>
+        <v>-14.943</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.31</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5088</v>
+        <v>0.5656</v>
       </c>
       <c r="J27" t="n">
-        <v>15.264</v>
+        <v>16.968</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.22</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4153</v>
+        <v>0.4577</v>
       </c>
       <c r="J28" t="n">
-        <v>12.459</v>
+        <v>13.731</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.97</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0509</v>
+        <v>-0.0589</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.527</v>
+        <v>-1.767</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1011</v>
+        <v>-0.1123</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.033</v>
+        <v>-3.369</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.62</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4119</v>
+        <v>-0.4205</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.357</v>
+        <v>-12.615</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.73</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1273</v>
+        <v>1.2377</v>
       </c>
       <c r="J32" t="n">
-        <v>27.0552</v>
+        <v>29.7048</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.42</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7461</v>
+        <v>0.8295</v>
       </c>
       <c r="J33" t="n">
-        <v>17.9064</v>
+        <v>19.908</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.17</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4124</v>
+        <v>0.4579</v>
       </c>
       <c r="J34" t="n">
-        <v>9.897600000000001</v>
+        <v>10.9896</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.13</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3506</v>
+        <v>0.3703</v>
       </c>
       <c r="J35" t="n">
-        <v>8.414400000000001</v>
+        <v>8.8872</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.04</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0956</v>
+        <v>0.1213</v>
       </c>
       <c r="J36" t="n">
-        <v>2.2944</v>
+        <v>2.9112</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.22</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4805</v>
+        <v>0.5187</v>
       </c>
       <c r="J37" t="n">
-        <v>11.532</v>
+        <v>12.4488</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.78</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2325</v>
+        <v>-0.2516</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.58</v>
+        <v>-6.0384</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.73</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2793</v>
+        <v>-0.2977</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.7032</v>
+        <v>-7.1448</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.68</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3266</v>
+        <v>-0.3436</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.8384</v>
+        <v>-8.2464</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.49</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5039</v>
+        <v>-0.5121</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.0936</v>
+        <v>-12.2904</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>0.85</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1566</v>
+        <v>-0.1773</v>
       </c>
       <c r="J42" t="n">
-        <v>-3.4452</v>
+        <v>-3.9006</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.79</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2189</v>
+        <v>-0.2391</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.8158</v>
+        <v>-5.2602</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.78</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2288</v>
+        <v>-0.2488</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.0336</v>
+        <v>-5.4736</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.67</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.331</v>
+        <v>-0.3488</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.282</v>
+        <v>-7.6736</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.64</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3591</v>
+        <v>-0.3758</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.9002</v>
+        <v>-8.2676</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.69</v>
       </c>
       <c r="I47" t="n">
-        <v>1.0468</v>
+        <v>1.1582</v>
       </c>
       <c r="J47" t="n">
-        <v>23.0296</v>
+        <v>25.4804</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.65</v>
       </c>
       <c r="I48" t="n">
-        <v>1.0002</v>
+        <v>1.1086</v>
       </c>
       <c r="J48" t="n">
-        <v>22.0044</v>
+        <v>24.3892</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.48</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8002</v>
+        <v>0.8928</v>
       </c>
       <c r="J49" t="n">
-        <v>17.6044</v>
+        <v>19.6416</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.3</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.6464</v>
       </c>
       <c r="J50" t="n">
-        <v>12.6742</v>
+        <v>14.2208</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.16</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3771</v>
+        <v>0.4174</v>
       </c>
       <c r="J51" t="n">
-        <v>8.296200000000001</v>
+        <v>9.1828</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.18</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4237</v>
+        <v>0.4549</v>
       </c>
       <c r="J52" t="n">
-        <v>10.1688</v>
+        <v>10.9176</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.9</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1123</v>
+        <v>-0.1301</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.6952</v>
+        <v>-3.1224</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.88</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1348</v>
+        <v>-0.1529</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.2352</v>
+        <v>-3.6696</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.6</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4056</v>
+        <v>-0.4186</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.734400000000001</v>
+        <v>-10.0464</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.47</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.532</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.6168</v>
+        <v>-12.768</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.82</v>
       </c>
       <c r="I57" t="n">
-        <v>1.2476</v>
+        <v>1.3621</v>
       </c>
       <c r="J57" t="n">
-        <v>29.9424</v>
+        <v>32.6904</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.8</v>
       </c>
       <c r="I58" t="n">
-        <v>1.2236</v>
+        <v>1.337</v>
       </c>
       <c r="J58" t="n">
-        <v>29.3664</v>
+        <v>32.088</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.96</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2303</v>
+        <v>-0.2147</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.5272</v>
+        <v>-5.1528</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.91</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3874</v>
+        <v>-0.3624</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.297599999999999</v>
+        <v>-8.6976</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.78</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7386</v>
+        <v>-0.6794</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.7264</v>
+        <v>-16.3056</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.43</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0524</v>
+        <v>1.0028</v>
       </c>
       <c r="J62" t="n">
-        <v>26.31</v>
+        <v>25.07</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.2</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5611</v>
+        <v>0.5458</v>
       </c>
       <c r="J63" t="n">
-        <v>14.0275</v>
+        <v>13.645</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.15</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4387</v>
+        <v>0.4347</v>
       </c>
       <c r="J64" t="n">
-        <v>10.9675</v>
+        <v>10.8675</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.09</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2759</v>
+        <v>0.2851</v>
       </c>
       <c r="J65" t="n">
-        <v>6.8975</v>
+        <v>7.1275</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.09</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2759</v>
+        <v>0.2851</v>
       </c>
       <c r="J66" t="n">
-        <v>6.8975</v>
+        <v>7.1275</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.59</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0699</v>
+        <v>1.0293</v>
       </c>
       <c r="J67" t="n">
-        <v>26.7475</v>
+        <v>25.7325</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.89</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1415</v>
+        <v>-0.1553</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.5375</v>
+        <v>-3.8825</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.87</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.163</v>
+        <v>-0.1772</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.075</v>
+        <v>-4.43</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.77</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2647</v>
+        <v>-0.2786</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.6175</v>
+        <v>-6.965</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.71</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3228</v>
+        <v>-0.3354</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.07</v>
+        <v>-8.385</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.66</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3232</v>
+        <v>1.3014</v>
       </c>
       <c r="J72" t="n">
-        <v>34.4032</v>
+        <v>33.8364</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.31</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7991</v>
+        <v>0.7612</v>
       </c>
       <c r="J73" t="n">
-        <v>20.7766</v>
+        <v>19.7912</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.18</v>
       </c>
       <c r="I74" t="n">
-        <v>0.498</v>
+        <v>0.4921</v>
       </c>
       <c r="J74" t="n">
-        <v>12.948</v>
+        <v>12.7946</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.16</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4472</v>
+        <v>0.4462</v>
       </c>
       <c r="J75" t="n">
-        <v>11.6272</v>
+        <v>11.6012</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.05</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1348</v>
+        <v>0.1573</v>
       </c>
       <c r="J76" t="n">
-        <v>3.5048</v>
+        <v>4.0898</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.25</v>
       </c>
       <c r="I77" t="n">
-        <v>0.588</v>
+        <v>0.5605</v>
       </c>
       <c r="J77" t="n">
-        <v>15.288</v>
+        <v>14.573</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.9</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1212</v>
+        <v>-0.137</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.1512</v>
+        <v>-3.562</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.87</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1529</v>
+        <v>-0.1695</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.9754</v>
+        <v>-4.407</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.71</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3101</v>
+        <v>-0.3254</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.0626</v>
+        <v>-8.4604</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.6</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4137</v>
+        <v>-0.425</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.7562</v>
+        <v>-11.05</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.82</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4721</v>
+        <v>1.4658</v>
       </c>
       <c r="J82" t="n">
-        <v>30.9141</v>
+        <v>30.7818</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.8</v>
       </c>
       <c r="I83" t="n">
-        <v>1.4492</v>
+        <v>1.4417</v>
       </c>
       <c r="J83" t="n">
-        <v>30.4332</v>
+        <v>30.2757</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.49</v>
       </c>
       <c r="I84" t="n">
-        <v>1.0867</v>
+        <v>1.053</v>
       </c>
       <c r="J84" t="n">
-        <v>22.8207</v>
+        <v>22.113</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.25</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6312</v>
+        <v>0.6186</v>
       </c>
       <c r="J85" t="n">
-        <v>13.2552</v>
+        <v>12.9906</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.87</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5413</v>
+        <v>-0.495</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.3673</v>
+        <v>-10.395</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.8</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.1822</v>
+        <v>-0.2084</v>
       </c>
       <c r="J87" t="n">
-        <v>-3.8262</v>
+        <v>-4.3764</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.71</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2767</v>
+        <v>-0.2997</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.8107</v>
+        <v>-6.2937</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.71</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2767</v>
+        <v>-0.2997</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.8107</v>
+        <v>-6.2937</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.61</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.369</v>
+        <v>-0.3885</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.749</v>
+        <v>-8.1585</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.33</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6321</v>
+        <v>-0.634</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.2741</v>
+        <v>-13.314</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.36</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9474</v>
+        <v>0.8864</v>
       </c>
       <c r="J92" t="n">
-        <v>27.4746</v>
+        <v>25.7056</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.12</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3697</v>
+        <v>0.3693</v>
       </c>
       <c r="J93" t="n">
-        <v>10.7213</v>
+        <v>10.7097</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3428</v>
+        <v>0.3445</v>
       </c>
       <c r="J94" t="n">
-        <v>9.9412</v>
+        <v>9.990500000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.08</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2581</v>
+        <v>0.2658</v>
       </c>
       <c r="J95" t="n">
-        <v>7.4849</v>
+        <v>7.7082</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.05</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1661</v>
+        <v>0.1791</v>
       </c>
       <c r="J96" t="n">
-        <v>4.8169</v>
+        <v>5.1939</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.06</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1773</v>
+        <v>0.1814</v>
       </c>
       <c r="J97" t="n">
-        <v>5.1417</v>
+        <v>5.2606</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.03</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1055</v>
+        <v>0.1098</v>
       </c>
       <c r="J98" t="n">
-        <v>3.0595</v>
+        <v>3.1842</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.97</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0452</v>
+        <v>-0.0545</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.3108</v>
+        <v>-1.5805</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.91</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1166</v>
+        <v>-0.1304</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.3814</v>
+        <v>-3.7816</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.72</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3098</v>
+        <v>-0.3234</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.9842</v>
+        <v>-9.3786</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.32</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8534</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="J102" t="n">
-        <v>21.335</v>
+        <v>20.0725</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.19</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5435</v>
+        <v>0.5285</v>
       </c>
       <c r="J103" t="n">
-        <v>13.5875</v>
+        <v>13.2125</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.14</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4198</v>
+        <v>0.4158</v>
       </c>
       <c r="J104" t="n">
-        <v>10.495</v>
+        <v>10.395</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.11</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3403</v>
+        <v>0.3427</v>
       </c>
       <c r="J105" t="n">
-        <v>8.5075</v>
+        <v>8.567500000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.02</v>
       </c>
       <c r="I106" t="n">
-        <v>0.0585</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="J106" t="n">
-        <v>1.4625</v>
+        <v>1.885</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.04</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1444</v>
+        <v>0.1451</v>
       </c>
       <c r="J107" t="n">
-        <v>3.61</v>
+        <v>3.6275</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.96</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.053</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.325</v>
+        <v>-1.6175</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.86</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1652</v>
+        <v>-0.1814</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.13</v>
+        <v>-4.535</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.83</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1958</v>
+        <v>-0.2122</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.895</v>
+        <v>-5.305</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.77</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2555</v>
+        <v>-0.2714</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.3875</v>
+        <v>-6.785</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.34</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8946</v>
+        <v>0.8398</v>
       </c>
       <c r="J112" t="n">
-        <v>24.1542</v>
+        <v>22.6746</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.25</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6849</v>
+        <v>0.6555</v>
       </c>
       <c r="J113" t="n">
-        <v>18.4923</v>
+        <v>17.6985</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.14</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4173</v>
+        <v>0.4141</v>
       </c>
       <c r="J114" t="n">
-        <v>11.2671</v>
+        <v>11.1807</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.06</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1915</v>
+        <v>0.2048</v>
       </c>
       <c r="J115" t="n">
-        <v>5.1705</v>
+        <v>5.5296</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.06</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1915</v>
+        <v>0.2048</v>
       </c>
       <c r="J116" t="n">
-        <v>5.1705</v>
+        <v>5.5296</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.27</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6125</v>
+        <v>0.5849</v>
       </c>
       <c r="J117" t="n">
-        <v>16.5375</v>
+        <v>15.7923</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.92</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1016</v>
+        <v>-0.1159</v>
       </c>
       <c r="J118" t="n">
-        <v>-2.7432</v>
+        <v>-3.1293</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.86</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.165</v>
+        <v>-0.1813</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.455</v>
+        <v>-4.8951</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2256</v>
+        <v>-0.242</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.0912</v>
+        <v>-6.534</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.6</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4168</v>
+        <v>-0.4274</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.2536</v>
+        <v>-11.5398</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.31</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4158</v>
+        <v>0.4281</v>
       </c>
       <c r="J122" t="n">
-        <v>12.474</v>
+        <v>12.843</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.26</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3569</v>
+        <v>0.3715</v>
       </c>
       <c r="J123" t="n">
-        <v>10.707</v>
+        <v>11.145</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.25</v>
       </c>
       <c r="I124" t="n">
-        <v>0.345</v>
+        <v>0.36</v>
       </c>
       <c r="J124" t="n">
-        <v>10.35</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.15</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2231</v>
+        <v>0.2403</v>
       </c>
       <c r="J125" t="n">
-        <v>6.693</v>
+        <v>7.209</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.1953</v>
+        <v>-0.2048</v>
       </c>
       <c r="J126" t="n">
-        <v>-5.859</v>
+        <v>-6.144</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.47</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7116</v>
+        <v>0.6846</v>
       </c>
       <c r="J127" t="n">
-        <v>21.348</v>
+        <v>20.538</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.16</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2909</v>
+        <v>0.2944</v>
       </c>
       <c r="J128" t="n">
-        <v>8.727</v>
+        <v>8.832000000000001</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.08</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1668</v>
+        <v>0.1738</v>
       </c>
       <c r="J129" t="n">
-        <v>5.004</v>
+        <v>5.214</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.6</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4238</v>
+        <v>-0.433</v>
       </c>
       <c r="J130" t="n">
-        <v>-12.714</v>
+        <v>-12.99</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.44</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5682</v>
+        <v>-0.5696</v>
       </c>
       <c r="J131" t="n">
-        <v>-17.046</v>
+        <v>-17.088</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.33</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6612</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="J132" t="n">
-        <v>16.53</v>
+        <v>15.965</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.16</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3584</v>
+        <v>0.36</v>
       </c>
       <c r="J133" t="n">
-        <v>8.960000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2213</v>
+        <v>0.2294</v>
       </c>
       <c r="J134" t="n">
-        <v>5.5325</v>
+        <v>5.735</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.85</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1902</v>
+        <v>-0.2033</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.755</v>
+        <v>-5.0825</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.67</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3667</v>
+        <v>-0.3767</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.1675</v>
+        <v>-9.4175</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.48</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1412</v>
+        <v>1.0991</v>
       </c>
       <c r="J137" t="n">
-        <v>28.53</v>
+        <v>27.4775</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3224</v>
+        <v>0.3238</v>
       </c>
       <c r="J138" t="n">
-        <v>8.06</v>
+        <v>8.095000000000001</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.03</v>
       </c>
       <c r="I139" t="n">
-        <v>0.108</v>
+        <v>0.1205</v>
       </c>
       <c r="J139" t="n">
-        <v>2.7</v>
+        <v>3.0125</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.99</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0793</v>
+        <v>-0.0765</v>
       </c>
       <c r="J140" t="n">
-        <v>-1.9825</v>
+        <v>-1.9125</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.93</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2893</v>
+        <v>-0.2799</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.2325</v>
+        <v>-6.9975</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.5</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9032</v>
+        <v>0.8617</v>
       </c>
       <c r="J142" t="n">
-        <v>26.1928</v>
+        <v>24.9893</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.2</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4084</v>
+        <v>0.4117</v>
       </c>
       <c r="J143" t="n">
-        <v>11.8436</v>
+        <v>11.9393</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1658</v>
+        <v>0.179</v>
       </c>
       <c r="J144" t="n">
-        <v>4.8082</v>
+        <v>5.191</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.06</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1444</v>
+        <v>0.1578</v>
       </c>
       <c r="J145" t="n">
-        <v>4.1876</v>
+        <v>4.5762</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.75</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3007</v>
+        <v>-0.3107</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.7203</v>
+        <v>-9.010300000000001</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.27</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7809</v>
+        <v>0.7313</v>
       </c>
       <c r="J147" t="n">
-        <v>22.6461</v>
+        <v>21.2077</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.27</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7809</v>
+        <v>0.7313</v>
       </c>
       <c r="J148" t="n">
-        <v>22.6461</v>
+        <v>21.2077</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.99</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0618</v>
+        <v>-0.0644</v>
       </c>
       <c r="J149" t="n">
-        <v>-1.7922</v>
+        <v>-1.8676</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.95</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2073</v>
+        <v>-0.2072</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.0117</v>
+        <v>-6.0088</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.71</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.86</v>
+        <v>-0.7953</v>
       </c>
       <c r="J151" t="n">
-        <v>-24.94</v>
+        <v>-23.0637</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.87</v>
       </c>
       <c r="I152" t="n">
-        <v>1.5503</v>
+        <v>1.5446</v>
       </c>
       <c r="J152" t="n">
-        <v>37.2072</v>
+        <v>37.0704</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.56</v>
       </c>
       <c r="I153" t="n">
-        <v>1.1833</v>
+        <v>1.1555</v>
       </c>
       <c r="J153" t="n">
-        <v>28.3992</v>
+        <v>27.732</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.25</v>
       </c>
       <c r="I154" t="n">
-        <v>0.6494</v>
+        <v>0.6313</v>
       </c>
       <c r="J154" t="n">
-        <v>15.5856</v>
+        <v>15.1512</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.17</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4538</v>
+        <v>0.4561</v>
       </c>
       <c r="J155" t="n">
-        <v>10.8912</v>
+        <v>10.9464</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3194</v>
+        <v>-0.2936</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.6656</v>
+        <v>-7.0464</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.3</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7066</v>
+        <v>0.6635</v>
       </c>
       <c r="J157" t="n">
-        <v>16.9584</v>
+        <v>15.924</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0467</v>
+        <v>0.0338</v>
       </c>
       <c r="J158" t="n">
-        <v>1.1208</v>
+        <v>0.8112</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.72</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2948</v>
+        <v>-0.3117</v>
       </c>
       <c r="J159" t="n">
-        <v>-7.0752</v>
+        <v>-7.4808</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.67</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3424</v>
+        <v>-0.3577</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.217599999999999</v>
+        <v>-8.5848</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.43</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5644</v>
+        <v>-0.5679</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.5456</v>
+        <v>-13.6296</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>2.41</v>
       </c>
       <c r="I162" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J162" t="n">
-        <v>31.1746</v>
+        <v>32.9324</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.84</v>
       </c>
       <c r="I163" t="n">
-        <v>1.4509</v>
+        <v>1.4513</v>
       </c>
       <c r="J163" t="n">
-        <v>24.6653</v>
+        <v>24.6721</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.73</v>
       </c>
       <c r="I164" t="n">
-        <v>1.3335</v>
+        <v>1.3258</v>
       </c>
       <c r="J164" t="n">
-        <v>22.6695</v>
+        <v>22.5386</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.43</v>
       </c>
       <c r="I165" t="n">
-        <v>0.9715</v>
+        <v>0.9318</v>
       </c>
       <c r="J165" t="n">
-        <v>16.5155</v>
+        <v>15.8406</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.24</v>
       </c>
       <c r="I166" t="n">
-        <v>0.5536</v>
+        <v>0.5598</v>
       </c>
       <c r="J166" t="n">
-        <v>9.411199999999999</v>
+        <v>9.5166</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.58</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.2912</v>
+        <v>-0.3322</v>
       </c>
       <c r="J167" t="n">
-        <v>-4.9504</v>
+        <v>-5.6474</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.35</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.5507</v>
+        <v>-0.5677</v>
       </c>
       <c r="J168" t="n">
-        <v>-9.3619</v>
+        <v>-9.6509</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.32</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.5797</v>
+        <v>-0.5941</v>
       </c>
       <c r="J169" t="n">
-        <v>-9.854900000000001</v>
+        <v>-10.0997</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.31</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5899</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.0283</v>
+        <v>-10.2561</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.22</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6876</v>
+        <v>-0.6907</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.6892</v>
+        <v>-11.7419</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.77</v>
       </c>
       <c r="I172" t="n">
-        <v>1.4049</v>
+        <v>1.3966</v>
       </c>
       <c r="J172" t="n">
-        <v>28.098</v>
+        <v>27.932</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.72</v>
       </c>
       <c r="I173" t="n">
-        <v>1.3479</v>
+        <v>1.336</v>
       </c>
       <c r="J173" t="n">
-        <v>26.958</v>
+        <v>26.72</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.68</v>
       </c>
       <c r="I174" t="n">
-        <v>1.302</v>
+        <v>1.2871</v>
       </c>
       <c r="J174" t="n">
-        <v>26.04</v>
+        <v>25.742</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.37</v>
       </c>
       <c r="I175" t="n">
-        <v>0.8914</v>
+        <v>0.8499</v>
       </c>
       <c r="J175" t="n">
-        <v>17.828</v>
+        <v>16.998</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.96</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2825</v>
+        <v>-0.2514</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.65</v>
+        <v>-5.028</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I177" t="n">
-        <v>0.0065</v>
+        <v>-0.0272</v>
       </c>
       <c r="J177" t="n">
-        <v>0.13</v>
+        <v>-0.544</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.73</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2471</v>
+        <v>-0.2729</v>
       </c>
       <c r="J178" t="n">
-        <v>-4.942</v>
+        <v>-5.458</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.57</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3997</v>
+        <v>-0.4188</v>
       </c>
       <c r="J179" t="n">
-        <v>-7.994</v>
+        <v>-8.375999999999999</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.48</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4834</v>
+        <v>-0.4974</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.667999999999999</v>
+        <v>-9.948</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.27</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6847</v>
+        <v>-0.6827</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.694</v>
+        <v>-13.654</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.72</v>
       </c>
       <c r="I182" t="n">
-        <v>1.3817</v>
+        <v>1.3658</v>
       </c>
       <c r="J182" t="n">
-        <v>30.3974</v>
+        <v>30.0476</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.39</v>
       </c>
       <c r="I183" t="n">
-        <v>0.958</v>
+        <v>0.9062</v>
       </c>
       <c r="J183" t="n">
-        <v>21.076</v>
+        <v>19.9364</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.2</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5355</v>
+        <v>0.5284</v>
       </c>
       <c r="J184" t="n">
-        <v>11.781</v>
+        <v>11.6248</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.17</v>
       </c>
       <c r="I185" t="n">
-        <v>0.4604</v>
+        <v>0.4607</v>
       </c>
       <c r="J185" t="n">
-        <v>10.1288</v>
+        <v>10.1354</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.16</v>
       </c>
       <c r="I186" t="n">
-        <v>0.4347</v>
+        <v>0.4375</v>
       </c>
       <c r="J186" t="n">
-        <v>9.5634</v>
+        <v>9.625</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0924</v>
+        <v>0.0674</v>
       </c>
       <c r="J187" t="n">
-        <v>2.0328</v>
+        <v>1.4828</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.76</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2459</v>
+        <v>-0.2661</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.4098</v>
+        <v>-5.8542</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.64</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3566</v>
+        <v>-0.3739</v>
       </c>
       <c r="J189" t="n">
-        <v>-7.8452</v>
+        <v>-8.2258</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.64</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3566</v>
+        <v>-0.3739</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.8452</v>
+        <v>-8.2258</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.61</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3847</v>
+        <v>-0.4007</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.4634</v>
+        <v>-8.8154</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.11</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3078</v>
+        <v>0.302</v>
       </c>
       <c r="J192" t="n">
-        <v>9.234</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1</v>
       </c>
       <c r="I193" t="n">
-        <v>0.028</v>
+        <v>0.0202</v>
       </c>
       <c r="J193" t="n">
-        <v>0.84</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.91</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1113</v>
+        <v>-0.1265</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.339</v>
+        <v>-3.795</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.68</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.34</v>
+        <v>-0.3541</v>
       </c>
       <c r="J195" t="n">
-        <v>-10.2</v>
+        <v>-10.623</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.68</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.34</v>
+        <v>-0.3541</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.2</v>
+        <v>-10.623</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.42</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0359</v>
+        <v>0.9837</v>
       </c>
       <c r="J197" t="n">
-        <v>31.077</v>
+        <v>29.511</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.21</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5661</v>
       </c>
       <c r="J198" t="n">
-        <v>17.496</v>
+        <v>16.983</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.2</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5451</v>
       </c>
       <c r="J199" t="n">
-        <v>16.8</v>
+        <v>16.353</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.19</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5363</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="J200" t="n">
-        <v>16.089</v>
+        <v>15.711</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.99</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1041</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J201" t="n">
-        <v>-3.123</v>
+        <v>-2.814</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.5</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1507</v>
+        <v>1.1124</v>
       </c>
       <c r="J202" t="n">
-        <v>33.3703</v>
+        <v>32.2596</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.3</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8042</v>
+        <v>0.7604</v>
       </c>
       <c r="J203" t="n">
-        <v>23.3218</v>
+        <v>22.0516</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.03</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0935</v>
+        <v>0.1104</v>
       </c>
       <c r="J204" t="n">
-        <v>2.7115</v>
+        <v>3.2016</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.02</v>
       </c>
       <c r="I205" t="n">
-        <v>0.0564</v>
+        <v>0.074</v>
       </c>
       <c r="J205" t="n">
-        <v>1.6356</v>
+        <v>2.146</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.97</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1728</v>
+        <v>-0.1651</v>
       </c>
       <c r="J206" t="n">
-        <v>-5.0112</v>
+        <v>-4.7879</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.23</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5392</v>
+        <v>0.518</v>
       </c>
       <c r="J207" t="n">
-        <v>15.6368</v>
+        <v>15.022</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.9</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1235</v>
+        <v>-0.1387</v>
       </c>
       <c r="J208" t="n">
-        <v>-3.5815</v>
+        <v>-4.0223</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.84</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1852</v>
+        <v>-0.2017</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.3708</v>
+        <v>-5.8493</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.78</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2452</v>
+        <v>-0.2614</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.1108</v>
+        <v>-7.5806</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3321</v>
+        <v>-0.3462</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.6309</v>
+        <v>-10.0398</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3460/event_3460_evp_summary.xlsx
+++ b/database/event/3460/event_3460_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8351</v>
+        <v>5.8272</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0042</v>
+        <v>2.0015</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0321</v>
+        <v>2.0488</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8351</v>
+        <v>5.8272</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5172</v>
+        <v>2.5861</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3179</v>
+        <v>3.2411</v>
       </c>
       <c r="H2" t="n">
-        <v>3.411</v>
+        <v>3.2666</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8419</v>
+        <v>1.8341</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3179</v>
+        <v>3.2411</v>
       </c>
       <c r="K2" t="n">
         <v>102</v>
@@ -529,7 +529,7 @@
         <v>103</v>
       </c>
       <c r="M2" t="n">
-        <v>5.1598</v>
+        <v>5.0752</v>
       </c>
       <c r="N2" t="n">
         <v>205</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.621</v>
+        <v>5.6031</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9307</v>
+        <v>1.9245</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9346</v>
+        <v>1.9467</v>
       </c>
       <c r="E3" t="n">
-        <v>5.621</v>
+        <v>5.6031</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6073</v>
+        <v>2.6531</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0137</v>
+        <v>2.95</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7084</v>
+        <v>3.5181</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0025</v>
+        <v>1.9753</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0137</v>
+        <v>2.95</v>
       </c>
       <c r="K3" t="n">
         <v>102</v>
@@ -575,7 +575,7 @@
         <v>103</v>
       </c>
       <c r="M3" t="n">
-        <v>5.0162</v>
+        <v>4.9253</v>
       </c>
       <c r="N3" t="n">
         <v>205</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.671</v>
+        <v>4.7027</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6044</v>
+        <v>1.6153</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5021</v>
+        <v>1.5365</v>
       </c>
       <c r="E4" t="n">
-        <v>4.671</v>
+        <v>4.7027</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6768</v>
+        <v>2.7222</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9942</v>
+        <v>1.9805</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9375</v>
+        <v>3.7776</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1262</v>
+        <v>2.121</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9942</v>
+        <v>1.9805</v>
       </c>
       <c r="K4" t="n">
         <v>51</v>
@@ -621,7 +621,7 @@
         <v>111</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1204</v>
+        <v>4.1015</v>
       </c>
       <c r="N4" t="n">
         <v>162</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.635</v>
+        <v>3.716</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2485</v>
+        <v>1.2763</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0305</v>
+        <v>1.087</v>
       </c>
       <c r="E5" t="n">
-        <v>3.635</v>
+        <v>3.716</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4269</v>
+        <v>2.5198</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2081</v>
+        <v>1.1962</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1132</v>
+        <v>3.018</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6811</v>
+        <v>1.6945</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2081</v>
+        <v>1.1962</v>
       </c>
       <c r="K5" t="n">
         <v>102</v>
@@ -667,7 +667,7 @@
         <v>103</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8892</v>
+        <v>2.8907</v>
       </c>
       <c r="N5" t="n">
         <v>205</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.4881</v>
+        <v>3.4916</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1981</v>
+        <v>1.1993</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9637</v>
+        <v>0.9848</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4881</v>
+        <v>3.4916</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4038</v>
+        <v>2.4517</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0843</v>
+        <v>1.0399</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0369</v>
+        <v>2.7622</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6399</v>
+        <v>1.5509</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0843</v>
+        <v>1.0399</v>
       </c>
       <c r="K6" t="n">
         <v>92</v>
@@ -713,7 +713,7 @@
         <v>54</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7242</v>
+        <v>2.5908</v>
       </c>
       <c r="N6" t="n">
         <v>146</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4814</v>
+        <v>3.3737</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1958</v>
+        <v>1.1588</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9606</v>
+        <v>0.9311</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4814</v>
+        <v>3.3737</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2753</v>
+        <v>3.2017</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2061</v>
+        <v>0.172</v>
       </c>
       <c r="H7" t="n">
-        <v>5.9121</v>
+        <v>5.578</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1925</v>
+        <v>3.1319</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2061</v>
+        <v>0.172</v>
       </c>
       <c r="K7" t="n">
         <v>92</v>
@@ -759,7 +759,7 @@
         <v>54</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3986</v>
+        <v>3.3039</v>
       </c>
       <c r="N7" t="n">
         <v>146</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1579</v>
+        <v>3.1569</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0847</v>
+        <v>1.0843</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8133</v>
+        <v>0.8323</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1579</v>
+        <v>3.1569</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6164</v>
+        <v>2.6738</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5415</v>
+        <v>0.4831</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7382</v>
+        <v>3.5961</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0186</v>
+        <v>2.0191</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5415</v>
+        <v>0.4831</v>
       </c>
       <c r="K8" t="n">
         <v>51</v>
@@ -805,7 +805,7 @@
         <v>111</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5601</v>
+        <v>2.5022</v>
       </c>
       <c r="N8" t="n">
         <v>162</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.6808</v>
+        <v>2.7258</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9208</v>
+        <v>0.9362</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5962</v>
+        <v>0.6359</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6808</v>
+        <v>2.7258</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0728</v>
+        <v>3.0862</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.392</v>
+        <v>-0.3604</v>
       </c>
       <c r="H9" t="n">
-        <v>5.244</v>
+        <v>5.1444</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8317</v>
+        <v>2.8884</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.392</v>
+        <v>-0.3604</v>
       </c>
       <c r="K9" t="n">
         <v>44</v>
@@ -851,7 +851,7 @@
         <v>46</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4397</v>
+        <v>2.528</v>
       </c>
       <c r="N9" t="n">
         <v>90</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.606</v>
+        <v>2.6403</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8951</v>
+        <v>0.9069</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5621</v>
+        <v>0.597</v>
       </c>
       <c r="E10" t="n">
-        <v>2.606</v>
+        <v>2.6403</v>
       </c>
       <c r="F10" t="n">
-        <v>3.016</v>
+        <v>3.0158</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.41</v>
+        <v>-0.3755</v>
       </c>
       <c r="H10" t="n">
-        <v>5.0567</v>
+        <v>4.8799</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7306</v>
+        <v>2.7399</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.41</v>
+        <v>-0.3755</v>
       </c>
       <c r="K10" t="n">
         <v>92</v>
@@ -897,7 +897,7 @@
         <v>54</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3206</v>
+        <v>2.3644</v>
       </c>
       <c r="N10" t="n">
         <v>146</v>
@@ -906,185 +906,185 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5703</v>
+        <v>2.4962</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8828</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.5314</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5703</v>
+        <v>2.4962</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6728</v>
+        <v>2.9457</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8975</v>
+        <v>-0.4495</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6728</v>
+        <v>4.617</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3633</v>
+        <v>2.5923</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8975</v>
+        <v>-0.4495</v>
       </c>
       <c r="K11" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="L11" t="n">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2608</v>
+        <v>2.1428</v>
       </c>
       <c r="N11" t="n">
-        <v>162</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4369</v>
+        <v>2.4667</v>
       </c>
       <c r="C12" t="n">
-        <v>0.837</v>
+        <v>0.8472</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4851</v>
+        <v>0.5179</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4369</v>
+        <v>2.4667</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9158</v>
+        <v>0.651</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4789</v>
+        <v>1.8157</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7262</v>
+        <v>0.651</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5521</v>
+        <v>0.3655</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4789</v>
+        <v>1.8157</v>
       </c>
       <c r="K12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="L12" t="n">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0732</v>
+        <v>2.1812</v>
       </c>
       <c r="N12" t="n">
-        <v>90</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4311</v>
+        <v>2.3073</v>
       </c>
       <c r="C13" t="n">
-        <v>0.835</v>
+        <v>0.7925</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4825</v>
+        <v>0.4453</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4311</v>
+        <v>2.3073</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9922</v>
+        <v>2.2575</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4389</v>
+        <v>0.0498</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9922</v>
+        <v>2.2575</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5358000000000001</v>
+        <v>1.2675</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4389</v>
+        <v>0.0498</v>
       </c>
       <c r="K13" t="n">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="L13" t="n">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9747</v>
+        <v>1.3173</v>
       </c>
       <c r="N13" t="n">
-        <v>205</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2955</v>
+        <v>2.3072</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7884</v>
+        <v>0.7925</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4208</v>
+        <v>0.4453</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2955</v>
+        <v>2.3072</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2164</v>
+        <v>0.9368</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0791</v>
+        <v>1.3704</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4186</v>
+        <v>0.9368</v>
       </c>
       <c r="I14" t="n">
-        <v>1.306</v>
+        <v>0.526</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0791</v>
+        <v>1.3704</v>
       </c>
       <c r="K14" t="n">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="L14" t="n">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3851</v>
+        <v>1.8964</v>
       </c>
       <c r="N14" t="n">
-        <v>90</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1657</v>
+        <v>2.0994</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7439</v>
+        <v>0.7211</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3617</v>
+        <v>0.3506</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1657</v>
+        <v>2.0994</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0146</v>
+        <v>0.883</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1511</v>
+        <v>1.2164</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0146</v>
+        <v>0.883</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.4958</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1511</v>
+        <v>1.2164</v>
       </c>
       <c r="K15" t="n">
         <v>51</v>
@@ -1127,7 +1127,7 @@
         <v>111</v>
       </c>
       <c r="M15" t="n">
-        <v>1.699</v>
+        <v>1.7122</v>
       </c>
       <c r="N15" t="n">
         <v>162</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0355</v>
+        <v>1.9878</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.6828</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3024</v>
+        <v>0.2997</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0355</v>
+        <v>1.9878</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0355</v>
+        <v>1.9878</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0355</v>
+        <v>1.9878</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0355</v>
+        <v>1.9878</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0355</v>
+        <v>1.9878</v>
       </c>
       <c r="N16" t="n">
         <v>123</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9332</v>
+        <v>1.9638</v>
       </c>
       <c r="C17" t="n">
-        <v>0.664</v>
+        <v>0.6745</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2558</v>
+        <v>0.2888</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9332</v>
+        <v>1.9638</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8658</v>
+        <v>2.8889</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9326</v>
+        <v>-0.9251</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5612</v>
+        <v>4.4036</v>
       </c>
       <c r="I17" t="n">
-        <v>2.463</v>
+        <v>2.4725</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9326</v>
+        <v>-0.9251</v>
       </c>
       <c r="K17" t="n">
         <v>92</v>
@@ -1219,7 +1219,7 @@
         <v>54</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5304</v>
+        <v>1.5474</v>
       </c>
       <c r="N17" t="n">
         <v>146</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8394</v>
+        <v>1.9561</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6318</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2131</v>
+        <v>0.2853</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8394</v>
+        <v>1.9561</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2419</v>
+        <v>2.3307</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4025</v>
+        <v>-0.3746</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5026</v>
+        <v>2.3307</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3514</v>
+        <v>1.3086</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4025</v>
+        <v>-0.3746</v>
       </c>
       <c r="K18" t="n">
         <v>92</v>
@@ -1265,7 +1265,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9488999999999999</v>
+        <v>0.9339999999999999</v>
       </c>
       <c r="N18" t="n">
         <v>146</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4126</v>
+        <v>1.3886</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4852</v>
+        <v>0.4769</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0188</v>
+        <v>0.0268</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4126</v>
+        <v>1.3886</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4126</v>
+        <v>1.959</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.5704</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4126</v>
+        <v>1.959</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4126</v>
+        <v>1.0999</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.5704</v>
       </c>
       <c r="K19" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4126</v>
+        <v>0.5295000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>164</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3345</v>
+        <v>1.2486</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4584</v>
+        <v>0.4289</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0167</v>
+        <v>-0.037</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3345</v>
+        <v>1.2486</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9304</v>
+        <v>1.2486</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5959</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9304</v>
+        <v>1.2486</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0424</v>
+        <v>1.2486</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5959</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>44</v>
+        <v>164</v>
       </c>
       <c r="L20" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4465</v>
+        <v>1.2486</v>
       </c>
       <c r="N20" t="n">
-        <v>90</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.198</v>
+        <v>1.1116</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4115</v>
+        <v>0.3818</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0788</v>
+        <v>-0.0994</v>
       </c>
       <c r="E21" t="n">
-        <v>1.198</v>
+        <v>1.1116</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1824</v>
+        <v>2.0772</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.9656</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3065</v>
+        <v>2.0772</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2455</v>
+        <v>1.1663</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.9656</v>
       </c>
       <c r="K21" t="n">
         <v>102</v>
@@ -1403,7 +1403,7 @@
         <v>103</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2611</v>
+        <v>0.2006999999999999</v>
       </c>
       <c r="N21" t="n">
         <v>205</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0611</v>
+        <v>0.8972</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3645</v>
+        <v>0.3082</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1412</v>
+        <v>-0.1971</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0611</v>
+        <v>0.8972</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0611</v>
+        <v>0.8972</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0611</v>
+        <v>0.8972</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0611</v>
+        <v>0.8972</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0611</v>
+        <v>0.8972</v>
       </c>
       <c r="N22" t="n">
         <v>113</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8102</v>
+        <v>0.6688</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2783</v>
+        <v>0.2297</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2554</v>
+        <v>-0.3011</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8102</v>
+        <v>0.6688</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8102</v>
+        <v>0.6688</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8102</v>
+        <v>0.6688</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8102</v>
+        <v>0.6688</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8102</v>
+        <v>0.6688</v>
       </c>
       <c r="N23" t="n">
         <v>113</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.697</v>
+        <v>0.6328</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2394</v>
+        <v>0.2174</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3069</v>
+        <v>-0.3175</v>
       </c>
       <c r="E24" t="n">
-        <v>0.697</v>
+        <v>0.6328</v>
       </c>
       <c r="F24" t="n">
-        <v>0.697</v>
+        <v>0.6328</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.697</v>
+        <v>0.6328</v>
       </c>
       <c r="I24" t="n">
-        <v>0.697</v>
+        <v>0.6328</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.697</v>
+        <v>0.6328</v>
       </c>
       <c r="N24" t="n">
         <v>113</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5851</v>
+        <v>0.492</v>
       </c>
       <c r="C25" t="n">
-        <v>0.201</v>
+        <v>0.169</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3579</v>
+        <v>-0.3817</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5851</v>
+        <v>0.492</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5851</v>
+        <v>0.492</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5851</v>
+        <v>0.492</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5851</v>
+        <v>0.492</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5851</v>
+        <v>0.492</v>
       </c>
       <c r="N25" t="n">
         <v>123</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5185</v>
+        <v>0.3946</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1781</v>
+        <v>0.1355</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3882</v>
+        <v>-0.426</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5185</v>
+        <v>0.3946</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5185</v>
+        <v>0.3946</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5185</v>
+        <v>0.3946</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5185</v>
+        <v>0.3946</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5185</v>
+        <v>0.3946</v>
       </c>
       <c r="N26" t="n">
         <v>113</v>
@@ -1642,124 +1642,124 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2588</v>
+        <v>0.2813</v>
       </c>
       <c r="C27" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5064</v>
+        <v>-0.4776</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2588</v>
+        <v>0.2813</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9902</v>
+        <v>0.2813</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.7314000000000001</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9902</v>
+        <v>0.2813</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5347</v>
+        <v>0.2813</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.7314000000000001</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>51</v>
+        <v>164</v>
       </c>
       <c r="L27" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1967000000000001</v>
+        <v>0.2813</v>
       </c>
       <c r="N27" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.237</v>
+        <v>0.2279</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0814</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5163</v>
+        <v>-0.502</v>
       </c>
       <c r="E28" t="n">
-        <v>0.237</v>
+        <v>0.2279</v>
       </c>
       <c r="F28" t="n">
-        <v>0.237</v>
+        <v>0.8677</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.6398</v>
       </c>
       <c r="H28" t="n">
-        <v>0.237</v>
+        <v>0.8677</v>
       </c>
       <c r="I28" t="n">
-        <v>0.237</v>
+        <v>0.4872</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.6398</v>
       </c>
       <c r="K28" t="n">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="M28" t="n">
-        <v>0.237</v>
+        <v>-0.1526</v>
       </c>
       <c r="N28" t="n">
-        <v>123</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1973</v>
+        <v>0.2185</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0678</v>
+        <v>0.075</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5344</v>
+        <v>-0.5063</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1973</v>
+        <v>0.2185</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1973</v>
+        <v>0.2185</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1973</v>
+        <v>0.2185</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1973</v>
+        <v>0.2185</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1973</v>
+        <v>0.2185</v>
       </c>
       <c r="N29" t="n">
         <v>123</v>
@@ -1780,139 +1780,139 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1758</v>
+        <v>0.1701</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0604</v>
+        <v>0.0584</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5442</v>
+        <v>-0.5283</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1758</v>
+        <v>0.1701</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1758</v>
+        <v>0.1701</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1758</v>
+        <v>0.1701</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1758</v>
+        <v>0.1701</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1758</v>
+        <v>0.1701</v>
       </c>
       <c r="N30" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NEKIZ</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0393</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0135</v>
+        <v>0.0246</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6063</v>
+        <v>-0.5732</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0393</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0393</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0393</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0393</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0393</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>69</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>NEKIZ</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0375</v>
+        <v>-0.0771</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0129</v>
+        <v>-0.0265</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6071</v>
+        <v>-0.6409</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0375</v>
+        <v>-0.0771</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0375</v>
+        <v>-0.0771</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0375</v>
+        <v>-0.0771</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0375</v>
+        <v>-0.0771</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>164</v>
+        <v>69</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0375</v>
+        <v>-0.0771</v>
       </c>
       <c r="N32" t="n">
-        <v>164</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0266</v>
+        <v>-0.0305</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6594</v>
+        <v>-0.6463</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7035</v>
+        <v>0.6798</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.7808</v>
+        <v>-0.7687</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7035</v>
+        <v>0.6798</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3799</v>
+        <v>0.3817</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.7808</v>
+        <v>-0.7687</v>
       </c>
       <c r="K33" t="n">
         <v>44</v>
@@ -1955,7 +1955,7 @@
         <v>46</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4009</v>
+        <v>-0.3870000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>90</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3742</v>
+        <v>-0.3842</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1285</v>
+        <v>-0.132</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7945</v>
+        <v>-0.7808</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3742</v>
+        <v>-0.3842</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3742</v>
+        <v>-0.3842</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3742</v>
+        <v>-0.3842</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3742</v>
+        <v>-0.3842</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3742</v>
+        <v>-0.3842</v>
       </c>
       <c r="N34" t="n">
         <v>113</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7849</v>
+        <v>-0.7267</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2696</v>
+        <v>-0.2496</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9815</v>
+        <v>-0.9368</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7849</v>
+        <v>-0.7267</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7849</v>
+        <v>-0.7267</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7849</v>
+        <v>-0.7267</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7849</v>
+        <v>-0.7267</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7849</v>
+        <v>-0.7267</v>
       </c>
       <c r="N35" t="n">
         <v>69</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8209</v>
+        <v>-0.7554</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.282</v>
+        <v>-0.2595</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9979</v>
+        <v>-0.9499</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8209</v>
+        <v>-0.7554</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8209</v>
+        <v>-0.7554</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8209</v>
+        <v>-0.7554</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8209</v>
+        <v>-0.7554</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8209</v>
+        <v>-0.7554</v>
       </c>
       <c r="N36" t="n">
         <v>164</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8744</v>
+        <v>-0.8539</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3003</v>
+        <v>-0.2933</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0222</v>
+        <v>-0.9948</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8744</v>
+        <v>-0.8539</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8744</v>
+        <v>-0.8539</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8744</v>
+        <v>-0.8539</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8744</v>
+        <v>-0.8539</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8744</v>
+        <v>-0.8539</v>
       </c>
       <c r="N37" t="n">
         <v>69</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8832</v>
+        <v>-0.8983</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3034</v>
+        <v>-0.3085</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0263</v>
+        <v>-1.015</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8832</v>
+        <v>-0.8983</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8832</v>
+        <v>-0.8983</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8832</v>
+        <v>-0.8983</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8832</v>
+        <v>-0.8983</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8832</v>
+        <v>-0.8983</v>
       </c>
       <c r="N38" t="n">
-        <v>123</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9222</v>
+        <v>-0.9187</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3168</v>
+        <v>-0.3155</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.044</v>
+        <v>-1.0243</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9222</v>
+        <v>-0.9187</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9222</v>
+        <v>-0.9187</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9222</v>
+        <v>-0.9187</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9222</v>
+        <v>-0.9187</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9222</v>
+        <v>-0.9187</v>
       </c>
       <c r="N39" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2121</v>
+        <v>-1.1966</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4163</v>
+        <v>-0.411</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.176</v>
+        <v>-1.1509</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2121</v>
+        <v>-1.1966</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2121</v>
+        <v>-1.1966</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2121</v>
+        <v>-1.1966</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2121</v>
+        <v>-1.1966</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2121</v>
+        <v>-1.1966</v>
       </c>
       <c r="N40" t="n">
         <v>69</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.632</v>
+        <v>-1.6324</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5605</v>
+        <v>-0.5607</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3671</v>
+        <v>-1.3494</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.632</v>
+        <v>-1.6324</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.632</v>
+        <v>-1.6324</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.632</v>
+        <v>-1.6324</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.632</v>
+        <v>-1.6324</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.632</v>
+        <v>-1.6324</v>
       </c>
       <c r="N41" t="n">
         <v>164</v>
@@ -2429,10 +2429,10 @@
         <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8184</v>
+        <v>0.7639</v>
       </c>
       <c r="J2" t="n">
-        <v>24.552</v>
+        <v>22.917</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7181</v>
+        <v>0.6599</v>
       </c>
       <c r="J3" t="n">
-        <v>21.543</v>
+        <v>19.797</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.12</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2745</v>
+        <v>0.2294</v>
       </c>
       <c r="J4" t="n">
-        <v>8.234999999999999</v>
+        <v>6.882</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0872</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>2.616</v>
+        <v>1.983</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.58</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4633</v>
+        <v>-0.4618</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.899</v>
+        <v>-13.854</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7914</v>
+        <v>0.7642</v>
       </c>
       <c r="J7" t="n">
-        <v>23.742</v>
+        <v>22.926</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.48</v>
+        <v>0.4384</v>
       </c>
       <c r="J8" t="n">
-        <v>14.4</v>
+        <v>13.152</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.98</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1077</v>
+        <v>-0.0823</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.231</v>
+        <v>-2.469</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.91</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.325</v>
+        <v>-0.283</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.75</v>
+        <v>-8.49</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.9</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3519</v>
+        <v>-0.3093</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.557</v>
+        <v>-9.279</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.55</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9433</v>
+        <v>0.898</v>
       </c>
       <c r="J12" t="n">
-        <v>25.4691</v>
+        <v>24.246</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4182</v>
+        <v>0.3618</v>
       </c>
       <c r="J13" t="n">
-        <v>11.2914</v>
+        <v>9.768599999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1621</v>
+        <v>0.1284</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3767</v>
+        <v>3.4668</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.8</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2591</v>
+        <v>-0.2398</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.9957</v>
+        <v>-6.4746</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.77</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2884</v>
+        <v>-0.2704</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.7868</v>
+        <v>-7.3008</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.53</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2252</v>
+        <v>1.246</v>
       </c>
       <c r="J17" t="n">
-        <v>33.0804</v>
+        <v>33.642</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.17</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4905</v>
+        <v>0.4513</v>
       </c>
       <c r="J18" t="n">
-        <v>13.2435</v>
+        <v>12.1851</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.02</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2437</v>
+        <v>1.7739</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2517</v>
+        <v>-0.2128</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.7959</v>
+        <v>-5.7456</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.9</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.364</v>
+        <v>-0.3216</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.827999999999999</v>
+        <v>-8.683199999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.32</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7373</v>
+        <v>0.722</v>
       </c>
       <c r="J22" t="n">
-        <v>22.119</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.07</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2547</v>
+        <v>0.2173</v>
       </c>
       <c r="J23" t="n">
-        <v>7.641</v>
+        <v>6.519</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.02</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0752</v>
       </c>
       <c r="J24" t="n">
-        <v>2.901</v>
+        <v>2.256</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.87</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4243</v>
+        <v>-0.3812</v>
       </c>
       <c r="J25" t="n">
-        <v>-12.729</v>
+        <v>-11.436</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.84</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4981</v>
+        <v>-0.4559</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.943</v>
+        <v>-13.677</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.31</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5656</v>
+        <v>0.5395</v>
       </c>
       <c r="J27" t="n">
-        <v>16.968</v>
+        <v>16.185</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.22</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4577</v>
+        <v>0.4067</v>
       </c>
       <c r="J28" t="n">
-        <v>13.731</v>
+        <v>12.201</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.97</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0589</v>
+        <v>-0.0461</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.767</v>
+        <v>-1.383</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1123</v>
+        <v>-0.0944</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.369</v>
+        <v>-2.832</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.62</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4205</v>
+        <v>-0.4125</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.615</v>
+        <v>-12.375</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.73</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2377</v>
+        <v>1.2364</v>
       </c>
       <c r="J32" t="n">
-        <v>29.7048</v>
+        <v>29.6736</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.42</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8295</v>
+        <v>0.8159</v>
       </c>
       <c r="J33" t="n">
-        <v>19.908</v>
+        <v>19.5816</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.17</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4579</v>
+        <v>0.4339</v>
       </c>
       <c r="J34" t="n">
-        <v>10.9896</v>
+        <v>10.4136</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.13</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3703</v>
+        <v>0.3382</v>
       </c>
       <c r="J35" t="n">
-        <v>8.8872</v>
+        <v>8.1168</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.04</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1213</v>
+        <v>0.0975</v>
       </c>
       <c r="J36" t="n">
-        <v>2.9112</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.22</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5187</v>
+        <v>0.5004</v>
       </c>
       <c r="J37" t="n">
-        <v>12.4488</v>
+        <v>12.0096</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.78</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2516</v>
+        <v>-0.2347</v>
       </c>
       <c r="J38" t="n">
-        <v>-6.0384</v>
+        <v>-5.6328</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.73</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2977</v>
+        <v>-0.2811</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.1448</v>
+        <v>-6.7464</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.68</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3436</v>
+        <v>-0.3285</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.2464</v>
+        <v>-7.884</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.49</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5121</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.2904</v>
+        <v>-12.3024</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>0.85</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1773</v>
+        <v>-0.1617</v>
       </c>
       <c r="J42" t="n">
-        <v>-3.9006</v>
+        <v>-3.5574</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.79</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2391</v>
+        <v>-0.2234</v>
       </c>
       <c r="J43" t="n">
-        <v>-5.2602</v>
+        <v>-4.9148</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.78</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2488</v>
+        <v>-0.2331</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.4736</v>
+        <v>-5.1282</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.67</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3488</v>
+        <v>-0.3345</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.6736</v>
+        <v>-7.359</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.64</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3758</v>
+        <v>-0.3629</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.2676</v>
+        <v>-7.9838</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.69</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1582</v>
+        <v>1.1535</v>
       </c>
       <c r="J47" t="n">
-        <v>25.4804</v>
+        <v>25.377</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.65</v>
       </c>
       <c r="I48" t="n">
-        <v>1.1086</v>
+        <v>1.1021</v>
       </c>
       <c r="J48" t="n">
-        <v>24.3892</v>
+        <v>24.2462</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.48</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8928</v>
+        <v>0.8838</v>
       </c>
       <c r="J49" t="n">
-        <v>19.6416</v>
+        <v>19.4436</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.3</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6464</v>
+        <v>0.6418</v>
       </c>
       <c r="J50" t="n">
-        <v>14.2208</v>
+        <v>14.1196</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.16</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4174</v>
+        <v>0.3867</v>
       </c>
       <c r="J51" t="n">
-        <v>9.1828</v>
+        <v>8.507400000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.18</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4549</v>
+        <v>0.4127</v>
       </c>
       <c r="J52" t="n">
-        <v>10.9176</v>
+        <v>9.9048</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.9</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1301</v>
+        <v>-0.115</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.1224</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.88</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1529</v>
+        <v>-0.137</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.6696</v>
+        <v>-3.288</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.6</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4186</v>
+        <v>-0.4087</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.0464</v>
+        <v>-9.8088</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.47</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.532</v>
+        <v>-0.5356</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.768</v>
+        <v>-12.8544</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.82</v>
       </c>
       <c r="I57" t="n">
-        <v>1.3621</v>
+        <v>1.3715</v>
       </c>
       <c r="J57" t="n">
-        <v>32.6904</v>
+        <v>32.916</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.8</v>
       </c>
       <c r="I58" t="n">
-        <v>1.337</v>
+        <v>1.3441</v>
       </c>
       <c r="J58" t="n">
-        <v>32.088</v>
+        <v>32.2584</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.96</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2147</v>
+        <v>-0.1811</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.1528</v>
+        <v>-4.3464</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.91</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3624</v>
+        <v>-0.3229</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.6976</v>
+        <v>-7.7496</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.78</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6794</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.3056</v>
+        <v>-15.6168</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.43</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="J62" t="n">
-        <v>25.07</v>
+        <v>25.005</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.2</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5458</v>
+        <v>0.5113</v>
       </c>
       <c r="J63" t="n">
-        <v>13.645</v>
+        <v>12.7825</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.15</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4347</v>
+        <v>0.3997</v>
       </c>
       <c r="J64" t="n">
-        <v>10.8675</v>
+        <v>9.9925</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.09</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2851</v>
+        <v>0.253</v>
       </c>
       <c r="J65" t="n">
-        <v>7.1275</v>
+        <v>6.325</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.09</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2851</v>
+        <v>0.253</v>
       </c>
       <c r="J66" t="n">
-        <v>7.1275</v>
+        <v>6.325</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.59</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0293</v>
+        <v>1.0101</v>
       </c>
       <c r="J67" t="n">
-        <v>25.7325</v>
+        <v>25.2525</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.89</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1553</v>
+        <v>-0.1357</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.8825</v>
+        <v>-3.3925</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.87</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1772</v>
+        <v>-0.157</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.43</v>
+        <v>-3.925</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.77</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2786</v>
+        <v>-0.2596</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.965</v>
+        <v>-6.49</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.71</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3354</v>
+        <v>-0.3194</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.385</v>
+        <v>-7.985</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.66</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3014</v>
+        <v>1.3208</v>
       </c>
       <c r="J72" t="n">
-        <v>33.8364</v>
+        <v>34.3408</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.31</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7612</v>
+        <v>0.7379</v>
       </c>
       <c r="J73" t="n">
-        <v>19.7912</v>
+        <v>19.1854</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.18</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4921</v>
+        <v>0.4604</v>
       </c>
       <c r="J74" t="n">
-        <v>12.7946</v>
+        <v>11.9704</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.16</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4462</v>
+        <v>0.414</v>
       </c>
       <c r="J75" t="n">
-        <v>11.6012</v>
+        <v>10.764</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.05</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1573</v>
+        <v>0.1314</v>
       </c>
       <c r="J76" t="n">
-        <v>4.0898</v>
+        <v>3.4164</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.25</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5605</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>14.573</v>
+        <v>13.1976</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.9</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.137</v>
+        <v>-0.1205</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.562</v>
+        <v>-3.133</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.87</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1695</v>
+        <v>-0.1515</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.407</v>
+        <v>-3.939</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.71</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3254</v>
+        <v>-0.3087</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.4604</v>
+        <v>-8.026199999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.6</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.425</v>
+        <v>-0.416</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.05</v>
+        <v>-10.816</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.82</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4658</v>
+        <v>1.495</v>
       </c>
       <c r="J82" t="n">
-        <v>30.7818</v>
+        <v>31.395</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.8</v>
       </c>
       <c r="I83" t="n">
-        <v>1.4417</v>
+        <v>1.4693</v>
       </c>
       <c r="J83" t="n">
-        <v>30.2757</v>
+        <v>30.8553</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.49</v>
       </c>
       <c r="I84" t="n">
-        <v>1.053</v>
+        <v>1.0653</v>
       </c>
       <c r="J84" t="n">
-        <v>22.113</v>
+        <v>22.3713</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.25</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6186</v>
+        <v>0.5949</v>
       </c>
       <c r="J85" t="n">
-        <v>12.9906</v>
+        <v>12.4929</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.87</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.495</v>
+        <v>-0.4627</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.395</v>
+        <v>-9.716699999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.8</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.2084</v>
+        <v>-0.1927</v>
       </c>
       <c r="J87" t="n">
-        <v>-4.3764</v>
+        <v>-4.0467</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.71</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2997</v>
+        <v>-0.2879</v>
       </c>
       <c r="J88" t="n">
-        <v>-6.2937</v>
+        <v>-6.0459</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.71</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2997</v>
+        <v>-0.2879</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.2937</v>
+        <v>-6.0459</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.61</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3885</v>
+        <v>-0.379</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.1585</v>
+        <v>-7.959</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.33</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.634</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.314</v>
+        <v>-13.6857</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.36</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8864</v>
+        <v>0.8671</v>
       </c>
       <c r="J92" t="n">
-        <v>25.7056</v>
+        <v>25.1459</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.12</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3693</v>
+        <v>0.333</v>
       </c>
       <c r="J93" t="n">
-        <v>10.7097</v>
+        <v>9.657</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3445</v>
+        <v>0.3089</v>
       </c>
       <c r="J94" t="n">
-        <v>9.990500000000001</v>
+        <v>8.9581</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.08</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2658</v>
+        <v>0.2333</v>
       </c>
       <c r="J95" t="n">
-        <v>7.7082</v>
+        <v>6.7657</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.05</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1791</v>
+        <v>0.1519</v>
       </c>
       <c r="J96" t="n">
-        <v>5.1939</v>
+        <v>4.4051</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.06</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1814</v>
+        <v>0.1421</v>
       </c>
       <c r="J97" t="n">
-        <v>5.2606</v>
+        <v>4.1209</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.03</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1098</v>
+        <v>0.081</v>
       </c>
       <c r="J98" t="n">
-        <v>3.1842</v>
+        <v>2.349</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.97</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0545</v>
+        <v>-0.0437</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.5805</v>
+        <v>-1.2673</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.91</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1304</v>
+        <v>-0.1125</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.7816</v>
+        <v>-3.2625</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.72</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3234</v>
+        <v>-0.3066</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.3786</v>
+        <v>-8.891400000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.32</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.7774</v>
       </c>
       <c r="J102" t="n">
-        <v>20.0725</v>
+        <v>19.435</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.19</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5285</v>
+        <v>0.4918</v>
       </c>
       <c r="J103" t="n">
-        <v>13.2125</v>
+        <v>12.295</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.14</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4158</v>
+        <v>0.3793</v>
       </c>
       <c r="J104" t="n">
-        <v>10.395</v>
+        <v>9.4825</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.11</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3427</v>
+        <v>0.3077</v>
       </c>
       <c r="J105" t="n">
-        <v>8.567500000000001</v>
+        <v>7.6925</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.02</v>
       </c>
       <c r="I106" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0589</v>
       </c>
       <c r="J106" t="n">
-        <v>1.885</v>
+        <v>1.4725</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.04</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1451</v>
+        <v>0.1111</v>
       </c>
       <c r="J107" t="n">
-        <v>3.6275</v>
+        <v>2.7775</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.96</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.0533</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.6175</v>
+        <v>-1.3325</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.86</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1814</v>
+        <v>-0.1623</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.535</v>
+        <v>-4.0575</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.83</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2122</v>
+        <v>-0.1926</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.305</v>
+        <v>-4.815</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.77</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2714</v>
+        <v>-0.2524</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.785</v>
+        <v>-6.31</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.34</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8398</v>
+        <v>0.8173</v>
       </c>
       <c r="J112" t="n">
-        <v>22.6746</v>
+        <v>22.0671</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.25</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6555</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="J113" t="n">
-        <v>17.6985</v>
+        <v>16.8075</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.14</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4141</v>
+        <v>0.3783</v>
       </c>
       <c r="J114" t="n">
-        <v>11.1807</v>
+        <v>10.2141</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.06</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2048</v>
+        <v>0.1761</v>
       </c>
       <c r="J115" t="n">
-        <v>5.5296</v>
+        <v>4.7547</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.06</v>
       </c>
       <c r="I116" t="n">
-        <v>0.2048</v>
+        <v>0.1761</v>
       </c>
       <c r="J116" t="n">
-        <v>5.5296</v>
+        <v>4.7547</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.27</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5849</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="J117" t="n">
-        <v>15.7923</v>
+        <v>14.3289</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.92</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1159</v>
+        <v>-0.1002</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.1293</v>
+        <v>-2.7054</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.86</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1813</v>
+        <v>-0.1622</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.8951</v>
+        <v>-4.3794</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.242</v>
+        <v>-0.2224</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.534</v>
+        <v>-6.0048</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.6</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4274</v>
+        <v>-0.4189</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.5398</v>
+        <v>-11.3103</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.31</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4281</v>
+        <v>0.3637</v>
       </c>
       <c r="J122" t="n">
-        <v>12.843</v>
+        <v>10.911</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.26</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3715</v>
+        <v>0.3113</v>
       </c>
       <c r="J123" t="n">
-        <v>11.145</v>
+        <v>9.339</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.25</v>
       </c>
       <c r="I124" t="n">
-        <v>0.36</v>
+        <v>0.3007</v>
       </c>
       <c r="J124" t="n">
-        <v>10.8</v>
+        <v>9.021000000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.15</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2403</v>
+        <v>0.1939</v>
       </c>
       <c r="J125" t="n">
-        <v>7.209</v>
+        <v>5.817</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2048</v>
+        <v>-0.1849</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.144</v>
+        <v>-5.547</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.47</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6846</v>
+        <v>0.7309</v>
       </c>
       <c r="J127" t="n">
-        <v>20.538</v>
+        <v>21.927</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.16</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2944</v>
+        <v>0.2822</v>
       </c>
       <c r="J128" t="n">
-        <v>8.832000000000001</v>
+        <v>8.465999999999999</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.08</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1738</v>
+        <v>0.1565</v>
       </c>
       <c r="J129" t="n">
-        <v>5.214</v>
+        <v>4.695</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.6</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.433</v>
+        <v>-0.4257</v>
       </c>
       <c r="J130" t="n">
-        <v>-12.99</v>
+        <v>-12.771</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.44</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5696</v>
+        <v>-0.581</v>
       </c>
       <c r="J131" t="n">
-        <v>-17.088</v>
+        <v>-17.43</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.33</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="J132" t="n">
-        <v>15.965</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.16</v>
       </c>
       <c r="I133" t="n">
-        <v>0.36</v>
+        <v>0.3057</v>
       </c>
       <c r="J133" t="n">
-        <v>9</v>
+        <v>7.6425</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2294</v>
+        <v>0.1856</v>
       </c>
       <c r="J134" t="n">
-        <v>5.735</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.85</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2033</v>
+        <v>-0.1826</v>
       </c>
       <c r="J135" t="n">
-        <v>-5.0825</v>
+        <v>-4.565</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.67</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3767</v>
+        <v>-0.3645</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.4175</v>
+        <v>-9.112500000000001</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.48</v>
       </c>
       <c r="I137" t="n">
-        <v>1.0991</v>
+        <v>1.1113</v>
       </c>
       <c r="J137" t="n">
-        <v>27.4775</v>
+        <v>27.7825</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3238</v>
+        <v>0.2871</v>
       </c>
       <c r="J138" t="n">
-        <v>8.095000000000001</v>
+        <v>7.1775</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.03</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1205</v>
+        <v>0.0983</v>
       </c>
       <c r="J139" t="n">
-        <v>3.0125</v>
+        <v>2.4575</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.99</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0765</v>
+        <v>-0.0562</v>
       </c>
       <c r="J140" t="n">
-        <v>-1.9125</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.93</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2799</v>
+        <v>-0.2396</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.9975</v>
+        <v>-5.99</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.5</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8617</v>
+        <v>0.8095</v>
       </c>
       <c r="J142" t="n">
-        <v>24.9893</v>
+        <v>23.4755</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.2</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4117</v>
+        <v>0.3565</v>
       </c>
       <c r="J143" t="n">
-        <v>11.9393</v>
+        <v>10.3385</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.179</v>
+        <v>0.1442</v>
       </c>
       <c r="J144" t="n">
-        <v>5.191</v>
+        <v>4.1818</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.06</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1578</v>
+        <v>0.1258</v>
       </c>
       <c r="J145" t="n">
-        <v>4.5762</v>
+        <v>3.6482</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.75</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3107</v>
+        <v>-0.2944</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.010300000000001</v>
+        <v>-8.537599999999999</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.27</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7313</v>
+        <v>0.6997</v>
       </c>
       <c r="J147" t="n">
-        <v>21.2077</v>
+        <v>20.2913</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.27</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7313</v>
+        <v>0.6997</v>
       </c>
       <c r="J148" t="n">
-        <v>21.2077</v>
+        <v>20.2913</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.99</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0644</v>
+        <v>-0.0463</v>
       </c>
       <c r="J149" t="n">
-        <v>-1.8676</v>
+        <v>-1.3427</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.95</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2072</v>
+        <v>-0.1714</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.0088</v>
+        <v>-4.9706</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.71</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7953</v>
+        <v>-0.7703</v>
       </c>
       <c r="J151" t="n">
-        <v>-23.0637</v>
+        <v>-22.3387</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.87</v>
       </c>
       <c r="I152" t="n">
-        <v>1.5446</v>
+        <v>1.5801</v>
       </c>
       <c r="J152" t="n">
-        <v>37.0704</v>
+        <v>37.9224</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.56</v>
       </c>
       <c r="I153" t="n">
-        <v>1.1555</v>
+        <v>1.17</v>
       </c>
       <c r="J153" t="n">
-        <v>27.732</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.25</v>
       </c>
       <c r="I154" t="n">
-        <v>0.6313</v>
+        <v>0.6062</v>
       </c>
       <c r="J154" t="n">
-        <v>15.1512</v>
+        <v>14.5488</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.17</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4561</v>
+        <v>0.4254</v>
       </c>
       <c r="J155" t="n">
-        <v>10.9464</v>
+        <v>10.2096</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2936</v>
+        <v>-0.259</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.0464</v>
+        <v>-6.216</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.3</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6635</v>
+        <v>0.619</v>
       </c>
       <c r="J157" t="n">
-        <v>15.924</v>
+        <v>14.856</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0338</v>
+        <v>0.028</v>
       </c>
       <c r="J158" t="n">
-        <v>0.8112</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.72</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3117</v>
+        <v>-0.2946</v>
       </c>
       <c r="J159" t="n">
-        <v>-7.4808</v>
+        <v>-7.0704</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.67</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3577</v>
+        <v>-0.343</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.5848</v>
+        <v>-8.231999999999999</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.43</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5679</v>
+        <v>-0.5772</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.6296</v>
+        <v>-13.8528</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>2.41</v>
       </c>
       <c r="I162" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J162" t="n">
-        <v>32.9324</v>
+        <v>33.6906</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.84</v>
       </c>
       <c r="I163" t="n">
-        <v>1.4513</v>
+        <v>1.485</v>
       </c>
       <c r="J163" t="n">
-        <v>24.6721</v>
+        <v>25.245</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.73</v>
       </c>
       <c r="I164" t="n">
-        <v>1.3258</v>
+        <v>1.3549</v>
       </c>
       <c r="J164" t="n">
-        <v>22.5386</v>
+        <v>23.0333</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.43</v>
       </c>
       <c r="I165" t="n">
-        <v>0.9318</v>
+        <v>0.9362</v>
       </c>
       <c r="J165" t="n">
-        <v>15.8406</v>
+        <v>15.9154</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.24</v>
       </c>
       <c r="I166" t="n">
-        <v>0.5598</v>
+        <v>0.532</v>
       </c>
       <c r="J166" t="n">
-        <v>9.5166</v>
+        <v>9.044</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.58</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.3322</v>
+        <v>-0.3121</v>
       </c>
       <c r="J167" t="n">
-        <v>-5.6474</v>
+        <v>-5.3057</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.35</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.5677</v>
+        <v>-0.5782</v>
       </c>
       <c r="J168" t="n">
-        <v>-9.6509</v>
+        <v>-9.8294</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.32</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.5941</v>
+        <v>-0.6055</v>
       </c>
       <c r="J169" t="n">
-        <v>-10.0997</v>
+        <v>-10.2935</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.31</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6032999999999999</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.2561</v>
+        <v>-10.4618</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.22</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6907</v>
+        <v>-0.7145</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.7419</v>
+        <v>-12.1465</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.77</v>
       </c>
       <c r="I172" t="n">
-        <v>1.3966</v>
+        <v>1.4223</v>
       </c>
       <c r="J172" t="n">
-        <v>27.932</v>
+        <v>28.446</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.72</v>
       </c>
       <c r="I173" t="n">
-        <v>1.336</v>
+        <v>1.3589</v>
       </c>
       <c r="J173" t="n">
-        <v>26.72</v>
+        <v>27.178</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.68</v>
       </c>
       <c r="I174" t="n">
-        <v>1.2871</v>
+        <v>1.3083</v>
       </c>
       <c r="J174" t="n">
-        <v>25.742</v>
+        <v>26.166</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.37</v>
       </c>
       <c r="I175" t="n">
-        <v>0.8499</v>
+        <v>0.8421</v>
       </c>
       <c r="J175" t="n">
-        <v>16.998</v>
+        <v>16.842</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.96</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2514</v>
+        <v>-0.2245</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.028</v>
+        <v>-4.49</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.0272</v>
+        <v>-0.0021</v>
       </c>
       <c r="J177" t="n">
-        <v>-0.544</v>
+        <v>-0.042</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.73</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2729</v>
+        <v>-0.2601</v>
       </c>
       <c r="J178" t="n">
-        <v>-5.458</v>
+        <v>-5.202</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.57</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.4188</v>
+        <v>-0.4116</v>
       </c>
       <c r="J179" t="n">
-        <v>-8.375999999999999</v>
+        <v>-8.231999999999999</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.48</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4974</v>
+        <v>-0.4954</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.948</v>
+        <v>-9.907999999999999</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.27</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6827</v>
+        <v>-0.7093</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.654</v>
+        <v>-14.186</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.72</v>
       </c>
       <c r="I182" t="n">
-        <v>1.3658</v>
+        <v>1.3886</v>
       </c>
       <c r="J182" t="n">
-        <v>30.0476</v>
+        <v>30.5492</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.39</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9062</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="J183" t="n">
-        <v>19.9364</v>
+        <v>19.6834</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.2</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5284</v>
+        <v>0.499</v>
       </c>
       <c r="J184" t="n">
-        <v>11.6248</v>
+        <v>10.978</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.17</v>
       </c>
       <c r="I185" t="n">
-        <v>0.4607</v>
+        <v>0.4297</v>
       </c>
       <c r="J185" t="n">
-        <v>10.1354</v>
+        <v>9.4534</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.16</v>
       </c>
       <c r="I186" t="n">
-        <v>0.4375</v>
+        <v>0.4062</v>
       </c>
       <c r="J186" t="n">
-        <v>9.625</v>
+        <v>8.936400000000001</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0674</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="J187" t="n">
-        <v>1.4828</v>
+        <v>1.4234</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.76</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2661</v>
+        <v>-0.251</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.8542</v>
+        <v>-5.522</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.64</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3739</v>
+        <v>-0.3611</v>
       </c>
       <c r="J189" t="n">
-        <v>-8.2258</v>
+        <v>-7.9442</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.64</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3739</v>
+        <v>-0.3611</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.2258</v>
+        <v>-7.9442</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.61</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4007</v>
+        <v>-0.3895</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.8154</v>
+        <v>-8.569000000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.11</v>
       </c>
       <c r="I192" t="n">
-        <v>0.302</v>
+        <v>0.2528</v>
       </c>
       <c r="J192" t="n">
-        <v>9.06</v>
+        <v>7.584</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1</v>
       </c>
       <c r="I193" t="n">
-        <v>0.0202</v>
+        <v>0.015</v>
       </c>
       <c r="J193" t="n">
-        <v>0.606</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.91</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1265</v>
+        <v>-0.1103</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.795</v>
+        <v>-3.309</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.68</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3541</v>
+        <v>-0.3392</v>
       </c>
       <c r="J195" t="n">
-        <v>-10.623</v>
+        <v>-10.176</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.68</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3541</v>
+        <v>-0.3392</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.623</v>
+        <v>-10.176</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.42</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9837</v>
+        <v>0.978</v>
       </c>
       <c r="J197" t="n">
-        <v>29.511</v>
+        <v>29.34</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.21</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5661</v>
+        <v>0.5325</v>
       </c>
       <c r="J198" t="n">
-        <v>16.983</v>
+        <v>15.975</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.2</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5451</v>
+        <v>0.5111</v>
       </c>
       <c r="J199" t="n">
-        <v>16.353</v>
+        <v>15.333</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.19</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.4894</v>
       </c>
       <c r="J200" t="n">
-        <v>15.711</v>
+        <v>14.682</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.99</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0728</v>
       </c>
       <c r="J201" t="n">
-        <v>-2.814</v>
+        <v>-2.184</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.5</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1124</v>
+        <v>1.1244</v>
       </c>
       <c r="J202" t="n">
-        <v>32.2596</v>
+        <v>32.6076</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.3</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7604</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="J203" t="n">
-        <v>22.0516</v>
+        <v>21.2396</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.03</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1104</v>
+        <v>0.0896</v>
       </c>
       <c r="J204" t="n">
-        <v>3.2016</v>
+        <v>2.5984</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.02</v>
       </c>
       <c r="I205" t="n">
-        <v>0.074</v>
+        <v>0.0575</v>
       </c>
       <c r="J205" t="n">
-        <v>2.146</v>
+        <v>1.6675</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.97</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1651</v>
+        <v>-0.1335</v>
       </c>
       <c r="J206" t="n">
-        <v>-4.7879</v>
+        <v>-3.8715</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.23</v>
       </c>
       <c r="I207" t="n">
-        <v>0.518</v>
+        <v>0.4628</v>
       </c>
       <c r="J207" t="n">
-        <v>15.022</v>
+        <v>13.4212</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.9</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1387</v>
+        <v>-0.1216</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.0223</v>
+        <v>-3.5264</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.84</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2017</v>
+        <v>-0.1823</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.8493</v>
+        <v>-5.2867</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.78</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2614</v>
+        <v>-0.2421</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.5806</v>
+        <v>-7.0209</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3462</v>
+        <v>-0.3307</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.0398</v>
+        <v>-9.590299999999999</v>
       </c>
     </row>
   </sheetData>
